--- a/docs/sketch/kahoot/unit1_L02.xlsx
+++ b/docs/sketch/kahoot/unit1_L02.xlsx
@@ -1589,7 +1589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA119"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13"/>
   <cols>
     <col width="12.5" customWidth="1" min="1" max="1"/>
@@ -5518,35 +5518,35 @@
       </c>
       <c r="B73" s="16" t="inlineStr">
         <is>
-          <t>Which renal process REDUCES the net elimination of a drug?</t>
+          <t>A heavy smoker on a CYP1A2-metabolized drug quits smoking abruptly. What should the PA anticipate?</t>
         </is>
       </c>
       <c r="C73" s="16" t="inlineStr">
         <is>
-          <t>Filtration of drug based on molecular size</t>
+          <t>Drug levels will fall because metabolism speeds up</t>
         </is>
       </c>
       <c r="D73" s="16" t="inlineStr">
         <is>
-          <t>Passive reabsorption of lipophilic, un-ionized drug</t>
+          <t>No change, since smoking affects only the lungs</t>
         </is>
       </c>
       <c r="E73" s="16" t="inlineStr">
         <is>
-          <t>Excretion of volatile agents by the lungs</t>
+          <t>The drug becomes a prodrug that needs activation</t>
         </is>
       </c>
       <c r="F73" s="16" t="inlineStr">
         <is>
-          <t>Glomerular filtration of free, unbound drug</t>
+          <t>Drug levels may rise as CYP1A induction fades</t>
         </is>
       </c>
       <c r="G73" s="14" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H73" s="18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I73" s="1" t="n"/>
@@ -5575,27 +5575,27 @@
       </c>
       <c r="B74" s="16" t="inlineStr">
         <is>
-          <t>Which statement correctly pairs each dose type with the parameter it is based on?</t>
+          <t>Which renal process REDUCES the net elimination of a drug?</t>
         </is>
       </c>
       <c r="C74" s="16" t="inlineStr">
         <is>
-          <t>Both loading and maintenance doses are based on half-life alone</t>
+          <t>Filtration of drug based on molecular size</t>
         </is>
       </c>
       <c r="D74" s="16" t="inlineStr">
         <is>
-          <t>Loading dose is based on Vd; maintenance dose is based on clearance</t>
+          <t>Excretion of volatile agents by the lungs</t>
         </is>
       </c>
       <c r="E74" s="16" t="inlineStr">
         <is>
-          <t>Loading dose is based on clearance; maintenance dose is based on Vd</t>
+          <t>Passive reabsorption of lipophilic, un-ionized drug</t>
         </is>
       </c>
       <c r="F74" s="16" t="inlineStr">
         <is>
-          <t>Both loading and maintenance doses are based on clearance alone</t>
+          <t>Glomerular filtration of free, unbound drug</t>
         </is>
       </c>
       <c r="G74" s="14" t="n">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="H74" s="18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I74" s="1" t="n"/>
@@ -5632,27 +5632,27 @@
       </c>
       <c r="B75" s="16" t="inlineStr">
         <is>
-          <t>A patient is about to start azathioprine. Testing shows TPMT deficiency. What is the main clinical concern?</t>
+          <t>Which statement correctly pairs each dose type with the parameter it is based on?</t>
         </is>
       </c>
       <c r="C75" s="16" t="inlineStr">
         <is>
-          <t>Faster CYP2D6 metabolism of the drug and lost effect</t>
+          <t>Both loading and maintenance doses are based on half-life alone</t>
         </is>
       </c>
       <c r="D75" s="16" t="inlineStr">
         <is>
-          <t>No concern, since genotype never affects therapy</t>
+          <t>Loading dose is based on Vd; maintenance dose is based on clearance</t>
         </is>
       </c>
       <c r="E75" s="16" t="inlineStr">
         <is>
-          <t>Severe HLA-associated hypersensitivity to the drug</t>
+          <t>Loading dose is based on clearance; maintenance dose is based on Vd</t>
         </is>
       </c>
       <c r="F75" s="16" t="inlineStr">
         <is>
-          <t>Increased risk of toxicity from the thiopurine drug</t>
+          <t>Both loading and maintenance doses are based on clearance alone</t>
         </is>
       </c>
       <c r="G75" s="14" t="n">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="H75" s="18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I75" s="1" t="n"/>
@@ -5689,27 +5689,27 @@
       </c>
       <c r="B76" s="16" t="inlineStr">
         <is>
-          <t>Which pairing of a genetic variant with the drug it most affects is correct?</t>
+          <t>A patient is about to start azathioprine. Testing shows TPMT deficiency. What is the main clinical concern?</t>
         </is>
       </c>
       <c r="C76" s="16" t="inlineStr">
         <is>
-          <t>CYP2D6 variation — azathioprine toxicity</t>
+          <t>Severe HLA-associated hypersensitivity to the drug</t>
         </is>
       </c>
       <c r="D76" s="16" t="inlineStr">
         <is>
-          <t>HLA-B*5801 — clopidogrel activation</t>
+          <t>No concern, since genotype never affects therapy</t>
         </is>
       </c>
       <c r="E76" s="16" t="inlineStr">
         <is>
-          <t>TPMT variation — codeine activation</t>
+          <t>Increased risk of toxicity from the thiopurine drug</t>
         </is>
       </c>
       <c r="F76" s="16" t="inlineStr">
         <is>
-          <t>CYP2C19 variation — clopidogrel activation</t>
+          <t>Faster CYP2D6 metabolism of the drug and lost effect</t>
         </is>
       </c>
       <c r="G76" s="14" t="n">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="H76" s="18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I76" s="1" t="n"/>
@@ -5746,27 +5746,27 @@
       </c>
       <c r="B77" s="16" t="inlineStr">
         <is>
-          <t>Which statement about using pharmacogenomic results best matches the lecture's personalized-pharmacotherapy model?</t>
+          <t>Which pairing of a genetic variant with the drug it most affects is correct?</t>
         </is>
       </c>
       <c r="C77" s="16" t="inlineStr">
         <is>
-          <t>Genotype is one input alongside phenotype, disease, and other drugs</t>
+          <t>TPMT variation — codeine activation</t>
         </is>
       </c>
       <c r="D77" s="16" t="inlineStr">
         <is>
-          <t>Genotype matters only for drugs that are given by the IV route</t>
+          <t>CYP2C19 variation — clopidogrel activation</t>
         </is>
       </c>
       <c r="E77" s="16" t="inlineStr">
         <is>
-          <t>Genotype becomes irrelevant once a drug reaches steady state</t>
+          <t>HLA-B*5801 — clopidogrel activation</t>
         </is>
       </c>
       <c r="F77" s="16" t="inlineStr">
         <is>
-          <t>Genotype alone should determine both the drug and its dose</t>
+          <t>CYP2D6 variation — azathioprine toxicity</t>
         </is>
       </c>
       <c r="G77" s="14" t="n">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="H77" s="18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I77" s="1" t="n"/>
@@ -5803,27 +5803,27 @@
       </c>
       <c r="B78" s="16" t="inlineStr">
         <is>
-          <t>NAPQI: which is right?</t>
+          <t>Which statement about using pharmacogenomic results best matches the lecture's personalized-pharmacotherapy model?</t>
         </is>
       </c>
       <c r="C78" s="16" t="inlineStr">
         <is>
-          <t>Toxic metabolite from acetaminophen via normal Phase I metabolism</t>
+          <t>Genotype is one input alongside phenotype, disease, and other drugs</t>
         </is>
       </c>
       <c r="D78" s="16" t="inlineStr">
         <is>
-          <t>Phase I often first — but some drugs go straight to conjugation</t>
+          <t>Genotype alone should determine both the drug and its dose</t>
         </is>
       </c>
       <c r="E78" s="16" t="inlineStr">
         <is>
-          <t>Time for plasma concentration to fall 50%; set by clearance + Vd</t>
+          <t>Genotype matters only for drugs that are given by the IV route</t>
         </is>
       </c>
       <c r="F78" s="16" t="inlineStr">
         <is>
-          <t>Clearance ↓ → t½ ↑ → concentration ↑ → time to steady state ↑</t>
+          <t>Genotype affects adverse-reaction risk but never drug metabolism</t>
         </is>
       </c>
       <c r="G78" s="14" t="n">
@@ -5860,27 +5860,27 @@
       </c>
       <c r="B79" s="16" t="inlineStr">
         <is>
-          <t>Phase order: which is right?</t>
+          <t>NAPQI: which is right?</t>
         </is>
       </c>
       <c r="C79" s="16" t="inlineStr">
         <is>
+          <t>Toxic metabolite from acetaminophen via normal Phase I metabolism</t>
+        </is>
+      </c>
+      <c r="D79" s="16" t="inlineStr">
+        <is>
           <t>Phase I often first — but some drugs go straight to conjugation</t>
         </is>
       </c>
-      <c r="D79" s="16" t="inlineStr">
-        <is>
-          <t>Toxic metabolite from acetaminophen via normal Phase I metabolism</t>
-        </is>
-      </c>
       <c r="E79" s="16" t="inlineStr">
         <is>
+          <t>Time for plasma concentration to fall 50%; set by clearance + Vd</t>
+        </is>
+      </c>
+      <c r="F79" s="16" t="inlineStr">
+        <is>
           <t>Clearance ↓ → t½ ↑ → concentration ↑ → time to steady state ↑</t>
-        </is>
-      </c>
-      <c r="F79" s="16" t="inlineStr">
-        <is>
-          <t>Time for plasma concentration to fall 50%; set by clearance + Vd</t>
         </is>
       </c>
       <c r="G79" s="14" t="n">
@@ -5917,27 +5917,27 @@
       </c>
       <c r="B80" s="16" t="inlineStr">
         <is>
-          <t>CYP enzyme inhibition: which is right?</t>
+          <t>Phase order: which is right?</t>
         </is>
       </c>
       <c r="C80" s="16" t="inlineStr">
         <is>
-          <t>&gt;50% of liver-metabolized prescription drugs</t>
+          <t>Phase I often first — but some drugs go straight to conjugation</t>
         </is>
       </c>
       <c r="D80" s="16" t="inlineStr">
         <is>
-          <t>Slows CYP → substrate level ↑ → toxicity risk</t>
+          <t>Toxic metabolite from acetaminophen via normal Phase I metabolism</t>
         </is>
       </c>
       <c r="E80" s="16" t="inlineStr">
         <is>
-          <t>Antidepressants, opioids — codeine activation</t>
+          <t>Clearance ↓ → t½ ↑ → concentration ↑ → time to steady state ↑</t>
         </is>
       </c>
       <c r="F80" s="16" t="inlineStr">
         <is>
-          <t>Active transporters move more drug into tubule</t>
+          <t>Time for plasma concentration to fall 50%; set by clearance + Vd</t>
         </is>
       </c>
       <c r="G80" s="14" t="n">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="H80" s="18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I80" s="1" t="n"/>
@@ -5974,27 +5974,27 @@
       </c>
       <c r="B81" s="16" t="inlineStr">
         <is>
-          <t>CYP enzyme induction: which is right?</t>
+          <t>CYP enzyme inhibition: which is right?</t>
         </is>
       </c>
       <c r="C81" s="16" t="inlineStr">
         <is>
-          <t>Genotype + phenotype + disease state + other medications</t>
+          <t>&gt;50% of liver-metabolized prescription drugs</t>
         </is>
       </c>
       <c r="D81" s="16" t="inlineStr">
         <is>
-          <t>More CYP made → substrate level ↓ → therapeutic failure</t>
+          <t>Slows CYP → substrate level ↑ → toxicity risk</t>
         </is>
       </c>
       <c r="E81" s="16" t="inlineStr">
         <is>
-          <t>Intake = elimination; ~4–5 half-lives, regardless of dose</t>
+          <t>Antidepressants, opioids — codeine activation</t>
         </is>
       </c>
       <c r="F81" s="16" t="inlineStr">
         <is>
-          <t>Clopidogrel activation; some antidepressant/PPI dosing</t>
+          <t>Active transporters move more drug into tubule</t>
         </is>
       </c>
       <c r="G81" s="14" t="n">
@@ -6031,27 +6031,27 @@
       </c>
       <c r="B82" s="16" t="inlineStr">
         <is>
-          <t>Figure 6 values: which is right?</t>
+          <t>CYP enzyme induction: which is right?</t>
         </is>
       </c>
       <c r="C82" s="16" t="inlineStr">
         <is>
-          <t>↑ Toxicity with thiopurines (azathioprine)</t>
+          <t>Genotype + phenotype + disease state + other medications</t>
         </is>
       </c>
       <c r="D82" s="16" t="inlineStr">
         <is>
-          <t>Inhibitor: 240% of baseline; inducer: 42%</t>
+          <t>More CYP made → substrate level ↓ → therapeutic failure</t>
         </is>
       </c>
       <c r="E82" s="16" t="inlineStr">
         <is>
-          <t>Competitive (not irreversible) antagonism</t>
+          <t>Intake = elimination; ~4–5 half-lives, regardless of dose</t>
         </is>
       </c>
       <c r="F82" s="16" t="inlineStr">
         <is>
-          <t>Minor; breast milk matters in lactation</t>
+          <t>Clopidogrel activation; some antidepressant/PPI dosing</t>
         </is>
       </c>
       <c r="G82" s="14" t="n">
@@ -6088,27 +6088,27 @@
       </c>
       <c r="B83" s="16" t="inlineStr">
         <is>
-          <t>CYP3A4 inhibitor + narrow-TI substrate: which is right?</t>
+          <t>Figure 6 values: which is right?</t>
         </is>
       </c>
       <c r="C83" s="16" t="inlineStr">
         <is>
-          <t>Ongoing dose to stay in range; based on clearance</t>
+          <t>↑ Toxicity with thiopurines (azathioprine)</t>
         </is>
       </c>
       <c r="D83" s="16" t="inlineStr">
         <is>
-          <t>Traps ionized drug in tubule, blocks reabsorption</t>
+          <t>Inhibitor: 240% of baseline; inducer: 42%</t>
         </is>
       </c>
       <c r="E83" s="16" t="inlineStr">
         <is>
-          <t>Larger first dose → target immediately; based on Vd</t>
+          <t>Competitive (not irreversible) antagonism</t>
         </is>
       </c>
       <c r="F83" s="16" t="inlineStr">
         <is>
-          <t>Level ↑ and toxicity risk ↑ — especially dangerous</t>
+          <t>P450 + reductase + NADPH + O₂ (smooth ER)</t>
         </is>
       </c>
       <c r="G83" s="14" t="n">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="H83" s="18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I83" s="1" t="n"/>
@@ -6145,35 +6145,35 @@
       </c>
       <c r="B84" s="16" t="inlineStr">
         <is>
-          <t>Main elimination route: which is right?</t>
+          <t>CYP3A4 inhibitor + narrow-TI substrate: which is right?</t>
         </is>
       </c>
       <c r="C84" s="16" t="inlineStr">
         <is>
-          <t>Kidney (most drugs and metabolites)</t>
+          <t>Simvastatin myopathy: lower dose or another statin</t>
         </is>
       </c>
       <c r="D84" s="16" t="inlineStr">
         <is>
-          <t>Volatile agents (anesthetic gases)</t>
+          <t>Ongoing dose to stay in range; based on clearance</t>
         </is>
       </c>
       <c r="E84" s="16" t="inlineStr">
         <is>
-          <t>50% / 25% / 12.5% / 6.25% / 3.125%</t>
+          <t>Traps ionized drug in tubule, blocks reabsorption</t>
         </is>
       </c>
       <c r="F84" s="16" t="inlineStr">
         <is>
-          <t>100% x (1/2)^(number of half-lives)</t>
+          <t>Level ↑ and toxicity risk ↑ — especially dangerous</t>
         </is>
       </c>
       <c r="G84" s="14" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H84" s="18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I84" s="1" t="n"/>
@@ -6202,27 +6202,27 @@
       </c>
       <c r="B85" s="16" t="inlineStr">
         <is>
-          <t>Bile / feces: which is right?</t>
+          <t>Main elimination route: which is right?</t>
         </is>
       </c>
       <c r="C85" s="16" t="inlineStr">
         <is>
-          <t>Some large or protein-bound drugs</t>
+          <t>Kidney (most drugs and metabolites)</t>
         </is>
       </c>
       <c r="D85" s="16" t="inlineStr">
         <is>
+          <t>Volatile agents (anesthetic gases)</t>
+        </is>
+      </c>
+      <c r="E85" s="16" t="inlineStr">
+        <is>
           <t>50% / 25% / 12.5% / 6.25% / 3.125%</t>
         </is>
       </c>
-      <c r="E85" s="16" t="inlineStr">
-        <is>
-          <t>Volatile agents (anesthetic gases)</t>
-        </is>
-      </c>
       <c r="F85" s="16" t="inlineStr">
         <is>
-          <t>Switch to prasugrel or ticagrelor</t>
+          <t>100% x (1/2)^(number of half-lives)</t>
         </is>
       </c>
       <c r="G85" s="14" t="n">
@@ -6259,27 +6259,27 @@
       </c>
       <c r="B86" s="16" t="inlineStr">
         <is>
-          <t>Lungs: which is right?</t>
+          <t>Bile / feces: which is right?</t>
         </is>
       </c>
       <c r="C86" s="16" t="inlineStr">
         <is>
+          <t>Some large or protein-bound drugs</t>
+        </is>
+      </c>
+      <c r="D86" s="16" t="inlineStr">
+        <is>
+          <t>50% / 25% / 12.5% / 6.25% / 3.125%</t>
+        </is>
+      </c>
+      <c r="E86" s="16" t="inlineStr">
+        <is>
           <t>Volatile agents (anesthetic gases)</t>
         </is>
       </c>
-      <c r="D86" s="16" t="inlineStr">
-        <is>
-          <t>100% x (1/2)^(number of half-lives)</t>
-        </is>
-      </c>
-      <c r="E86" s="16" t="inlineStr">
-        <is>
-          <t>50% / 25% / 12.5% / 6.25% / 3.125%</t>
-        </is>
-      </c>
       <c r="F86" s="16" t="inlineStr">
         <is>
-          <t>Some large or protein-bound drugs</t>
+          <t>Switch to prasugrel or ticagrelor</t>
         </is>
       </c>
       <c r="G86" s="14" t="n">
@@ -6316,27 +6316,27 @@
       </c>
       <c r="B87" s="16" t="inlineStr">
         <is>
-          <t>Sweat / breast milk: which is right?</t>
+          <t>Lungs: which is right?</t>
         </is>
       </c>
       <c r="C87" s="16" t="inlineStr">
         <is>
-          <t>Free (unbound) drug, by molecular size</t>
+          <t>Volatile agents (anesthetic gases)</t>
         </is>
       </c>
       <c r="D87" s="16" t="inlineStr">
         <is>
-          <t>Inhibitor: 240% of baseline; inducer: 42%</t>
+          <t>100% x (1/2)^(number of half-lives)</t>
         </is>
       </c>
       <c r="E87" s="16" t="inlineStr">
         <is>
-          <t>Minor; breast milk matters in lactation</t>
+          <t>50% / 25% / 12.5% / 6.25% / 3.125%</t>
         </is>
       </c>
       <c r="F87" s="16" t="inlineStr">
         <is>
-          <t>Severe hypersensitivity to allopurinol</t>
+          <t>Some large or protein-bound drugs</t>
         </is>
       </c>
       <c r="G87" s="14" t="n">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H87" s="18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I87" s="1" t="n"/>
@@ -6373,27 +6373,27 @@
       </c>
       <c r="B88" s="16" t="inlineStr">
         <is>
-          <t>Glomerular filtration: which is right?</t>
+          <t>Sweat / breast milk: which is right?</t>
         </is>
       </c>
       <c r="C88" s="16" t="inlineStr">
         <is>
-          <t>eGFR and creatinine clearance (CrCl)</t>
+          <t>Free (unbound) drug, by molecular size</t>
         </is>
       </c>
       <c r="D88" s="16" t="inlineStr">
         <is>
-          <t>Free (unbound) drug, by molecular size</t>
+          <t>CL × target concentration (÷ F orally)</t>
         </is>
       </c>
       <c r="E88" s="16" t="inlineStr">
         <is>
+          <t>Minor; breast milk matters in lactation</t>
+        </is>
+      </c>
+      <c r="F88" s="16" t="inlineStr">
+        <is>
           <t>Severe hypersensitivity to allopurinol</t>
-        </is>
-      </c>
-      <c r="F88" s="16" t="inlineStr">
-        <is>
-          <t>Minor; breast milk matters in lactation</t>
         </is>
       </c>
       <c r="G88" s="14" t="n">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="H88" s="18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I88" s="1" t="n"/>
@@ -6430,35 +6430,35 @@
       </c>
       <c r="B89" s="16" t="inlineStr">
         <is>
-          <t>Tubular secretion: which is right?</t>
+          <t>Glomerular filtration: which is right?</t>
         </is>
       </c>
       <c r="C89" s="16" t="inlineStr">
         <is>
-          <t>Slows CYP → substrate level ↑ → toxicity risk</t>
+          <t>Free (unbound) drug, by molecular size</t>
         </is>
       </c>
       <c r="D89" s="16" t="inlineStr">
         <is>
-          <t>Active transporters move more drug into tubule</t>
+          <t>Severe hypersensitivity to allopurinol</t>
         </is>
       </c>
       <c r="E89" s="16" t="inlineStr">
         <is>
-          <t>&gt;50% of liver-metabolized prescription drugs</t>
+          <t>CL × target concentration (÷ F orally)</t>
         </is>
       </c>
       <c r="F89" s="16" t="inlineStr">
         <is>
-          <t>Antidepressants, opioids — codeine activation</t>
+          <t>Minor; breast milk matters in lactation</t>
         </is>
       </c>
       <c r="G89" s="14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H89" s="18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I89" s="1" t="n"/>
@@ -6487,27 +6487,27 @@
       </c>
       <c r="B90" s="16" t="inlineStr">
         <is>
-          <t>Tubular reabsorption: which is right?</t>
+          <t>Tubular secretion: which is right?</t>
         </is>
       </c>
       <c r="C90" s="16" t="inlineStr">
         <is>
-          <t>Lipophilic, un-ionized drug diffuses back → less elimination</t>
+          <t>Slows CYP → substrate level ↑ → toxicity risk</t>
         </is>
       </c>
       <c r="D90" s="16" t="inlineStr">
         <is>
-          <t>Clearance ↓ → t½ ↑ → concentration ↑ → time to steady state ↑</t>
+          <t>Active transporters move more drug into tubule</t>
         </is>
       </c>
       <c r="E90" s="16" t="inlineStr">
         <is>
-          <t>Many antibiotics, digoxin, lithium — adjust dose or interval</t>
+          <t>&gt;50% of liver-metabolized prescription drugs</t>
         </is>
       </c>
       <c r="F90" s="16" t="inlineStr">
         <is>
-          <t>Phase I often first — but some drugs go straight to conjugation</t>
+          <t>Antidepressants, opioids — codeine activation</t>
         </is>
       </c>
       <c r="G90" s="14" t="n">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="H90" s="18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I90" s="1" t="n"/>
@@ -6544,27 +6544,27 @@
       </c>
       <c r="B91" s="16" t="inlineStr">
         <is>
-          <t>Alkalinize urine (aspirin overdose): which is right?</t>
+          <t>Tubular reabsorption: which is right?</t>
         </is>
       </c>
       <c r="C91" s="16" t="inlineStr">
         <is>
-          <t>Traps ionized drug in tubule, blocks reabsorption</t>
+          <t>Lipophilic, un-ionized drug diffuses back → less elimination</t>
         </is>
       </c>
       <c r="D91" s="16" t="inlineStr">
         <is>
-          <t>Level ↑ and toxicity risk ↑ — especially dangerous</t>
+          <t>Clearance ↓ → t½ ↑ → concentration ↑ → time to steady state ↑</t>
         </is>
       </c>
       <c r="E91" s="16" t="inlineStr">
         <is>
-          <t>Ongoing dose to stay in range; based on clearance</t>
+          <t>Many antibiotics, digoxin, lithium — adjust dose or interval</t>
         </is>
       </c>
       <c r="F91" s="16" t="inlineStr">
         <is>
-          <t>Review CYP450 interactions with current medications</t>
+          <t>Phase I often first — but some drugs go straight to conjugation</t>
         </is>
       </c>
       <c r="G91" s="14" t="n">
@@ -6601,31 +6601,31 @@
       </c>
       <c r="B92" s="16" t="inlineStr">
         <is>
-          <t>Renal function estimates: which is right?</t>
+          <t>Alkalinize urine (aspirin overdose): which is right?</t>
         </is>
       </c>
       <c r="C92" s="16" t="inlineStr">
         <is>
-          <t>eGFR and creatinine clearance (CrCl)</t>
+          <t>Traps ionized drug in tubule, blocks reabsorption</t>
         </is>
       </c>
       <c r="D92" s="16" t="inlineStr">
         <is>
-          <t>100% x (1/2)^(number of half-lives)</t>
+          <t>Level ↑ and toxicity risk ↑ — especially dangerous</t>
         </is>
       </c>
       <c r="E92" s="16" t="inlineStr">
         <is>
-          <t>Volatile agents (anesthetic gases)</t>
+          <t>Ongoing dose to stay in range; based on clearance</t>
         </is>
       </c>
       <c r="F92" s="16" t="inlineStr">
         <is>
-          <t>Kidney (most drugs and metabolites)</t>
+          <t>Hepatic CL ÷ hepatic blood flow; F ≈ f × (1 − ER)</t>
         </is>
       </c>
       <c r="G92" s="14" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H92" s="18" t="inlineStr">
         <is>
@@ -6658,35 +6658,35 @@
       </c>
       <c r="B93" s="16" t="inlineStr">
         <is>
-          <t>Renally cleared narrow-TI drugs: which is right?</t>
+          <t>Renal function estimates: which is right?</t>
         </is>
       </c>
       <c r="C93" s="16" t="inlineStr">
         <is>
-          <t>Clearance ↓ → t½ ↑ → concentration ↑ → time to steady state ↑</t>
+          <t>eGFR and creatinine clearance (CrCl)</t>
         </is>
       </c>
       <c r="D93" s="16" t="inlineStr">
         <is>
-          <t>Many antibiotics, digoxin, lithium — adjust dose or interval</t>
+          <t>100% x (1/2)^(number of half-lives)</t>
         </is>
       </c>
       <c r="E93" s="16" t="inlineStr">
         <is>
-          <t>Decrease dose and/or extend interval, guided by eGFR/CrCl</t>
+          <t>CL × target concentration (÷ F orally)</t>
         </is>
       </c>
       <c r="F93" s="16" t="inlineStr">
         <is>
-          <t>Lipophilic, un-ionized drug diffuses back → less elimination</t>
+          <t>Kidney (most drugs and metabolites)</t>
         </is>
       </c>
       <c r="G93" s="14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H93" s="18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I93" s="1" t="n"/>
@@ -6715,27 +6715,27 @@
       </c>
       <c r="B94" s="16" t="inlineStr">
         <is>
-          <t>CKD dosing: which is right?</t>
+          <t>Renally cleared narrow-TI drugs: which is right?</t>
         </is>
       </c>
       <c r="C94" s="16" t="inlineStr">
         <is>
-          <t>More CYP made → substrate level ↓ → therapeutic failure</t>
+          <t>Clearance ↓ → t½ ↑ → concentration ↑ → time to steady state ↑</t>
         </is>
       </c>
       <c r="D94" s="16" t="inlineStr">
         <is>
-          <t>Genotype + phenotype + disease state + other medications</t>
+          <t>Many antibiotics, digoxin, lithium — adjust dose or interval</t>
         </is>
       </c>
       <c r="E94" s="16" t="inlineStr">
         <is>
-          <t>Intake = elimination; ~4–5 half-lives, regardless of dose</t>
+          <t>Decrease dose and/or extend interval, guided by eGFR/CrCl</t>
         </is>
       </c>
       <c r="F94" s="16" t="inlineStr">
         <is>
-          <t>Decrease dose and/or extend interval, guided by eGFR/CrCl</t>
+          <t>Lipophilic, un-ionized drug diffuses back → less elimination</t>
         </is>
       </c>
       <c r="G94" s="14" t="n">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="H94" s="18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I94" s="1" t="n"/>
@@ -6772,27 +6772,27 @@
       </c>
       <c r="B95" s="16" t="inlineStr">
         <is>
-          <t>Half-life (t½): which is right?</t>
+          <t>CKD dosing: which is right?</t>
         </is>
       </c>
       <c r="C95" s="16" t="inlineStr">
         <is>
-          <t>Toxic metabolite from acetaminophen via normal Phase I metabolism</t>
+          <t>More CYP made → substrate level ↓ → therapeutic failure</t>
         </is>
       </c>
       <c r="D95" s="16" t="inlineStr">
         <is>
-          <t>Time for plasma concentration to fall 50%; set by clearance + Vd</t>
+          <t>Genotype + phenotype + disease state + other medications</t>
         </is>
       </c>
       <c r="E95" s="16" t="inlineStr">
         <is>
-          <t>Phase I often first — but some drugs go straight to conjugation</t>
+          <t>Intake = elimination; ~4–5 half-lives, regardless of dose</t>
         </is>
       </c>
       <c r="F95" s="16" t="inlineStr">
         <is>
-          <t>Clearance ↓ → t½ ↑ → concentration ↑ → time to steady state ↑</t>
+          <t>Decrease dose and/or extend interval, guided by eGFR/CrCl</t>
         </is>
       </c>
       <c r="G95" s="14" t="n">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="H95" s="18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I95" s="1" t="n"/>
@@ -6829,35 +6829,35 @@
       </c>
       <c r="B96" s="16" t="inlineStr">
         <is>
-          <t>% remaining formula: which is right?</t>
+          <t>Half-life (t½): which is right?</t>
         </is>
       </c>
       <c r="C96" s="16" t="inlineStr">
         <is>
-          <t>Kidney (most drugs and metabolites)</t>
+          <t>Toxic metabolite from acetaminophen via normal Phase I metabolism</t>
         </is>
       </c>
       <c r="D96" s="16" t="inlineStr">
         <is>
-          <t>eGFR and creatinine clearance (CrCl)</t>
+          <t>Time for plasma concentration to fall 50%; set by clearance + Vd</t>
         </is>
       </c>
       <c r="E96" s="16" t="inlineStr">
         <is>
-          <t>50% / 25% / 12.5% / 6.25% / 3.125%</t>
+          <t>Phase I often first — but some drugs go straight to conjugation</t>
         </is>
       </c>
       <c r="F96" s="16" t="inlineStr">
         <is>
-          <t>100% x (1/2)^(number of half-lives)</t>
+          <t>Clearance ↓ → t½ ↑ → concentration ↑ → time to steady state ↑</t>
         </is>
       </c>
       <c r="G96" s="14" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H96" s="18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I96" s="1" t="n"/>
@@ -6886,27 +6886,27 @@
       </c>
       <c r="B97" s="16" t="inlineStr">
         <is>
-          <t>Concentration formula: which is right?</t>
+          <t>% remaining formula: which is right?</t>
         </is>
       </c>
       <c r="C97" s="16" t="inlineStr">
         <is>
-          <t>After about 5 half-lives</t>
+          <t>Kidney (most drugs and metabolites)</t>
         </is>
       </c>
       <c r="D97" s="16" t="inlineStr">
         <is>
-          <t>Vd × target concentration</t>
+          <t>eGFR and creatinine clearance (CrCl)</t>
         </is>
       </c>
       <c r="E97" s="16" t="inlineStr">
         <is>
-          <t>Abacavir hypersensitivity</t>
+          <t>50% / 25% / 12.5% / 6.25% / 3.125%</t>
         </is>
       </c>
       <c r="F97" s="16" t="inlineStr">
         <is>
-          <t>C(t) = C₀ x (1/2)^(t/t½)</t>
+          <t>100% x (1/2)^(number of half-lives)</t>
         </is>
       </c>
       <c r="G97" s="14" t="n">
@@ -6943,27 +6943,27 @@
       </c>
       <c r="B98" s="16" t="inlineStr">
         <is>
-          <t>Remaining after 1/2/3/4/5 t½: which is right?</t>
+          <t>Concentration formula: which is right?</t>
         </is>
       </c>
       <c r="C98" s="16" t="inlineStr">
         <is>
-          <t>100% x (1/2)^(number of half-lives)</t>
+          <t>After about 5 half-lives</t>
         </is>
       </c>
       <c r="D98" s="16" t="inlineStr">
         <is>
-          <t>50% / 25% / 12.5% / 6.25% / 3.125%</t>
+          <t>Vd × target concentration</t>
         </is>
       </c>
       <c r="E98" s="16" t="inlineStr">
         <is>
-          <t>Volatile agents (anesthetic gases)</t>
+          <t>Abacavir hypersensitivity</t>
         </is>
       </c>
       <c r="F98" s="16" t="inlineStr">
         <is>
-          <t>Some large or protein-bound drugs</t>
+          <t>C(t) = C₀ x (1/2)^(t/t½)</t>
         </is>
       </c>
       <c r="G98" s="14" t="n">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="H98" s="18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I98" s="1" t="n"/>
@@ -7000,27 +7000,27 @@
       </c>
       <c r="B99" s="16" t="inlineStr">
         <is>
-          <t>~97% eliminated: which is right?</t>
+          <t>Remaining after 1/2/3/4/5 t½: which is right?</t>
         </is>
       </c>
       <c r="C99" s="16" t="inlineStr">
         <is>
-          <t>Abacavir hypersensitivity</t>
+          <t>100% x (1/2)^(number of half-lives)</t>
         </is>
       </c>
       <c r="D99" s="16" t="inlineStr">
         <is>
-          <t>Vd × target concentration</t>
+          <t>50% / 25% / 12.5% / 6.25% / 3.125%</t>
         </is>
       </c>
       <c r="E99" s="16" t="inlineStr">
         <is>
-          <t>C(t) = C₀ x (1/2)^(t/t½)</t>
+          <t>Volatile agents (anesthetic gases)</t>
         </is>
       </c>
       <c r="F99" s="16" t="inlineStr">
         <is>
-          <t>After about 5 half-lives</t>
+          <t>Some large or protein-bound drugs</t>
         </is>
       </c>
       <c r="G99" s="14" t="n">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="H99" s="18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I99" s="1" t="n"/>
@@ -7057,35 +7057,35 @@
       </c>
       <c r="B100" s="16" t="inlineStr">
         <is>
-          <t>Steady state: which is right?</t>
+          <t>~97% eliminated: which is right?</t>
         </is>
       </c>
       <c r="C100" s="16" t="inlineStr">
         <is>
-          <t>Intake = elimination; ~4–5 half-lives, regardless of dose</t>
+          <t>Abacavir hypersensitivity</t>
         </is>
       </c>
       <c r="D100" s="16" t="inlineStr">
         <is>
-          <t>More CYP made → substrate level ↓ → therapeutic failure</t>
+          <t>Vd × target concentration</t>
         </is>
       </c>
       <c r="E100" s="16" t="inlineStr">
         <is>
-          <t>Decrease dose and/or extend interval, guided by eGFR/CrCl</t>
+          <t>C(t) = C₀ x (1/2)^(t/t½)</t>
         </is>
       </c>
       <c r="F100" s="16" t="inlineStr">
         <is>
-          <t>Genotype + phenotype + disease state + other medications</t>
+          <t>After about 5 half-lives</t>
         </is>
       </c>
       <c r="G100" s="14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H100" s="18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I100" s="1" t="n"/>
@@ -7114,35 +7114,35 @@
       </c>
       <c r="B101" s="16" t="inlineStr">
         <is>
-          <t>Time to steady state set by: which is right?</t>
+          <t>Steady state: which is right?</t>
         </is>
       </c>
       <c r="C101" s="16" t="inlineStr">
         <is>
-          <t>After about 5 half-lives</t>
+          <t>Intake = elimination; ~4–5 half-lives, regardless of dose</t>
         </is>
       </c>
       <c r="D101" s="16" t="inlineStr">
         <is>
-          <t>t½ = 0.7 × Vd / CL</t>
+          <t>More CYP made → substrate level ↓ → therapeutic failure</t>
         </is>
       </c>
       <c r="E101" s="16" t="inlineStr">
         <is>
-          <t>C(t) = C₀ x (1/2)^(t/t½)</t>
+          <t>Decrease dose and/or extend interval, guided by eGFR/CrCl</t>
         </is>
       </c>
       <c r="F101" s="16" t="inlineStr">
         <is>
-          <t>Half-life</t>
+          <t>Genotype + phenotype + disease state + other medications</t>
         </is>
       </c>
       <c r="G101" s="14" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H101" s="18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I101" s="1" t="n"/>
@@ -7171,35 +7171,35 @@
       </c>
       <c r="B102" s="16" t="inlineStr">
         <is>
-          <t>Loading dose: which is right?</t>
+          <t>Time to steady state set by: which is right?</t>
         </is>
       </c>
       <c r="C102" s="16" t="inlineStr">
         <is>
-          <t>Level ↑ and toxicity risk ↑ — especially dangerous</t>
+          <t>Set by clearance alone</t>
         </is>
       </c>
       <c r="D102" s="16" t="inlineStr">
         <is>
-          <t>Larger first dose → target immediately; based on Vd</t>
+          <t>Induces CYP1A (AhR)</t>
         </is>
       </c>
       <c r="E102" s="16" t="inlineStr">
         <is>
-          <t>Ongoing dose to stay in range; based on clearance</t>
+          <t>t½ = 0.7 × Vd / CL</t>
         </is>
       </c>
       <c r="F102" s="16" t="inlineStr">
         <is>
-          <t>Review CYP450 interactions with current medications</t>
+          <t>Half-life</t>
         </is>
       </c>
       <c r="G102" s="14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H102" s="18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I102" s="1" t="n"/>
@@ -7228,27 +7228,27 @@
       </c>
       <c r="B103" s="16" t="inlineStr">
         <is>
-          <t>Maintenance dose: which is right?</t>
+          <t>Loading dose: which is right?</t>
         </is>
       </c>
       <c r="C103" s="16" t="inlineStr">
         <is>
-          <t>Traps ionized drug in tubule, blocks reabsorption</t>
+          <t>Level ↑ and toxicity risk ↑ — especially dangerous</t>
         </is>
       </c>
       <c r="D103" s="16" t="inlineStr">
         <is>
+          <t>Simvastatin myopathy: lower dose or another statin</t>
+        </is>
+      </c>
+      <c r="E103" s="16" t="inlineStr">
+        <is>
+          <t>Larger first dose → target immediately; based on Vd</t>
+        </is>
+      </c>
+      <c r="F103" s="16" t="inlineStr">
+        <is>
           <t>Review CYP450 interactions with current medications</t>
-        </is>
-      </c>
-      <c r="E103" s="16" t="inlineStr">
-        <is>
-          <t>Ongoing dose to stay in range; based on clearance</t>
-        </is>
-      </c>
-      <c r="F103" s="16" t="inlineStr">
-        <is>
-          <t>Level ↑ and toxicity risk ↑ — especially dangerous</t>
         </is>
       </c>
       <c r="G103" s="14" t="n">
@@ -7285,27 +7285,27 @@
       </c>
       <c r="B104" s="16" t="inlineStr">
         <is>
-          <t>CKD effect on PK: which is right?</t>
+          <t>Maintenance dose: which is right?</t>
         </is>
       </c>
       <c r="C104" s="16" t="inlineStr">
         <is>
-          <t>Phase I often first — but some drugs go straight to conjugation</t>
+          <t>Traps ionized drug in tubule, blocks reabsorption</t>
         </is>
       </c>
       <c r="D104" s="16" t="inlineStr">
         <is>
-          <t>Clearance ↓ → t½ ↑ → concentration ↑ → time to steady state ↑</t>
+          <t>Hepatic CL ÷ hepatic blood flow; F ≈ f × (1 − ER)</t>
         </is>
       </c>
       <c r="E104" s="16" t="inlineStr">
         <is>
-          <t>Lipophilic, un-ionized drug diffuses back → less elimination</t>
+          <t>Simvastatin myopathy: lower dose or another statin</t>
         </is>
       </c>
       <c r="F104" s="16" t="inlineStr">
         <is>
-          <t>Many antibiotics, digoxin, lithium — adjust dose or interval</t>
+          <t>Ongoing dose to stay in range; based on clearance</t>
         </is>
       </c>
       <c r="G104" s="14" t="n">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="H104" s="18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I104" s="1" t="n"/>
@@ -7342,27 +7342,27 @@
       </c>
       <c r="B105" s="16" t="inlineStr">
         <is>
-          <t>CYP2D6 variation: which is right?</t>
+          <t>CKD effect on PK: which is right?</t>
         </is>
       </c>
       <c r="C105" s="16" t="inlineStr">
         <is>
-          <t>Antidepressants, opioids — codeine activation</t>
+          <t>Phase I often first — but some drugs go straight to conjugation</t>
         </is>
       </c>
       <c r="D105" s="16" t="inlineStr">
         <is>
-          <t>Active transporters move more drug into tubule</t>
+          <t>Clearance ↓ → t½ ↑ → concentration ↑ → time to steady state ↑</t>
         </is>
       </c>
       <c r="E105" s="16" t="inlineStr">
         <is>
-          <t>Slows CYP → substrate level ↑ → toxicity risk</t>
+          <t>Lipophilic, un-ionized drug diffuses back → less elimination</t>
         </is>
       </c>
       <c r="F105" s="16" t="inlineStr">
         <is>
-          <t>&gt;50% of liver-metabolized prescription drugs</t>
+          <t>Many antibiotics, digoxin, lithium — adjust dose or interval</t>
         </is>
       </c>
       <c r="G105" s="14" t="n">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="H105" s="18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I105" s="1" t="n"/>
@@ -7399,27 +7399,27 @@
       </c>
       <c r="B106" s="16" t="inlineStr">
         <is>
-          <t>CYP2C19 variation: which is right?</t>
+          <t>CYP2D6 variation: which is right?</t>
         </is>
       </c>
       <c r="C106" s="16" t="inlineStr">
         <is>
-          <t>More CYP made → substrate level ↓ → therapeutic failure</t>
+          <t>Antidepressants, opioids — codeine activation</t>
         </is>
       </c>
       <c r="D106" s="16" t="inlineStr">
         <is>
-          <t>Genotype + phenotype + disease state + other medications</t>
+          <t>Active transporters move more drug into tubule</t>
         </is>
       </c>
       <c r="E106" s="16" t="inlineStr">
         <is>
-          <t>Clopidogrel activation; some antidepressant/PPI dosing</t>
+          <t>Slows CYP → substrate level ↑ → toxicity risk</t>
         </is>
       </c>
       <c r="F106" s="16" t="inlineStr">
         <is>
-          <t>Larger first dose → target immediately; based on Vd</t>
+          <t>&gt;50% of liver-metabolized prescription drugs</t>
         </is>
       </c>
       <c r="G106" s="14" t="n">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="H106" s="18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I106" s="1" t="n"/>
@@ -7456,27 +7456,27 @@
       </c>
       <c r="B107" s="16" t="inlineStr">
         <is>
-          <t>TPMT deficiency: which is right?</t>
+          <t>CYP2C19 variation: which is right?</t>
         </is>
       </c>
       <c r="C107" s="16" t="inlineStr">
         <is>
-          <t>↑ Toxicity with thiopurines (azathioprine)</t>
+          <t>More CYP made → substrate level ↓ → therapeutic failure</t>
         </is>
       </c>
       <c r="D107" s="16" t="inlineStr">
         <is>
-          <t>&gt;50% of liver-metabolized prescription drugs</t>
+          <t>Genotype + phenotype + disease state + other medications</t>
         </is>
       </c>
       <c r="E107" s="16" t="inlineStr">
         <is>
-          <t>Inhibitor: 240% of baseline; inducer: 42%</t>
+          <t>Clopidogrel activation; some antidepressant/PPI dosing</t>
         </is>
       </c>
       <c r="F107" s="16" t="inlineStr">
         <is>
-          <t>Competitive (not irreversible) antagonism</t>
+          <t>Larger first dose → target immediately; based on Vd</t>
         </is>
       </c>
       <c r="G107" s="14" t="n">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="H107" s="18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I107" s="1" t="n"/>
@@ -7513,35 +7513,35 @@
       </c>
       <c r="B108" s="16" t="inlineStr">
         <is>
-          <t>HLA-B*5801: which is right?</t>
+          <t>TPMT deficiency: which is right?</t>
         </is>
       </c>
       <c r="C108" s="16" t="inlineStr">
         <is>
-          <t>eGFR and creatinine clearance (CrCl)</t>
+          <t>↑ Toxicity with thiopurines (azathioprine)</t>
         </is>
       </c>
       <c r="D108" s="16" t="inlineStr">
         <is>
-          <t>Severe hypersensitivity to allopurinol</t>
+          <t>Inhibitor: 240% of baseline; inducer: 42%</t>
         </is>
       </c>
       <c r="E108" s="16" t="inlineStr">
         <is>
-          <t>Free (unbound) drug, by molecular size</t>
+          <t>Competitive (not irreversible) antagonism</t>
         </is>
       </c>
       <c r="F108" s="16" t="inlineStr">
         <is>
-          <t>Minor; breast milk matters in lactation</t>
+          <t>P450 + reductase + NADPH + O₂ (smooth ER)</t>
         </is>
       </c>
       <c r="G108" s="14" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H108" s="18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I108" s="1" t="n"/>
@@ -7570,35 +7570,35 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Personalized therapy inputs: which is right?</t>
+          <t>HLA-B*5801: which is right?</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Decrease dose and/or extend interval, guided by eGFR/CrCl</t>
+          <t>Severe hypersensitivity to allopurinol</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Genotype + phenotype + disease state + other medications</t>
+          <t>Free (unbound) drug, by molecular size</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>More CYP made → substrate level ↓ → therapeutic failure</t>
+          <t>Minor; breast milk matters in lactation</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Intake = elimination; ~4–5 half-lives, regardless of dose</t>
+          <t>CL × target concentration (÷ F orally)</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -7608,27 +7608,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Effect weakened, restored by higher agonist dose: which is right?</t>
+          <t>Personalized therapy inputs: which is right?</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Competitive (not irreversible) antagonism</t>
+          <t>Decrease dose and/or extend interval, guided by eGFR/CrCl</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>↑ Toxicity with thiopurines (azathioprine)</t>
+          <t>Genotype + phenotype + disease state + other medications</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Inhibitor: 240% of baseline; inducer: 42%</t>
+          <t>More CYP made → substrate level ↓ → therapeutic failure</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Minor; breast milk matters in lactation</t>
+          <t>Intake = elimination; ~4–5 half-lives, regardless of dose</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -7646,27 +7646,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Single best check vs. predictable toxicity: which is right?</t>
+          <t>Effect weakened, restored by higher agonist dose: which is right?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Traps ionized drug in tubule, blocks reabsorption</t>
+          <t>P450 + reductase + NADPH + O₂ (smooth ER)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Review CYP450 interactions with current medications</t>
+          <t>Competitive (not irreversible) antagonism</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Larger first dose → target immediately; based on Vd</t>
+          <t>↑ Toxicity with thiopurines (azathioprine)</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Level ↑ and toxicity risk ↑ — especially dangerous</t>
+          <t>Inhibitor: 240% of baseline; inducer: 42%</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -7684,35 +7684,35 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>t½ formula: which is right?</t>
+          <t>Single best check vs. predictable toxicity: which is right?</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Abacavir hypersensitivity</t>
+          <t>Simvastatin myopathy: lower dose or another statin</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>C(t) = C₀ x (1/2)^(t/t½)</t>
+          <t>Review CYP450 interactions with current medications</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>t½ = 0.7 × Vd / CL</t>
+          <t>Larger first dose → target immediately; based on Vd</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>After about 5 half-lives</t>
+          <t>Level ↑ and toxicity risk ↑ — especially dangerous</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -7722,27 +7722,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Loading dose formula: which is right?</t>
+          <t>t½ formula: which is right?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Vd × target concentration</t>
+          <t>Induces CYP1A (AhR)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
+          <t>Set by clearance alone</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>t½ = 0.7 × Vd / CL</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
           <t>After about 5 half-lives</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>C(t) = C₀ x (1/2)^(t/t½)</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Abacavir hypersensitivity</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -7750,7 +7750,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -7760,27 +7760,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>% of steady state: which is right?</t>
+          <t>Loading dose formula: which is right?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>1 t½ = 50% · 2 = 75% · 4 = &gt;90%</t>
+          <t>Vd × target concentration</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Some large or protein-bound drugs</t>
+          <t>After about 5 half-lives</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Switch to prasugrel or ticagrelor</t>
+          <t>C(t) = C₀ x (1/2)^(t/t½)</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>N-acetylcysteine within 8–16 h</t>
+          <t>Abacavir hypersensitivity</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -7798,22 +7798,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Saturable elimination: which is right?</t>
+          <t>% of steady state: which is right?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Phenytoin, ethanol, aspirin</t>
+          <t>1 t½ = 50% · 2 = 75% · 4 = &gt;90%</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Abacavir hypersensitivity</t>
+          <t>Some large or protein-bound drugs</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Vd × target concentration</t>
+          <t>Switch to prasugrel or ticagrelor</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -7836,31 +7836,31 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CYP3A4 share: which is right?</t>
+          <t>Saturable elimination: which is right?</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>&gt;50% of liver-metabolized prescription drugs</t>
+          <t>Phenytoin, ethanol, aspirin</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Active transporters move more drug into tubule</t>
+          <t>Abacavir hypersensitivity</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Slows CYP → substrate level ↑ → toxicity risk</t>
+          <t>At least 6 h after the dose</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Antidepressants, opioids — codeine activation</t>
+          <t>Vd × target concentration</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -7874,31 +7874,31 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Acetaminophen antidote: which is right?</t>
+          <t>CYP3A4 share: which is right?</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>N-acetylcysteine within 8–16 h</t>
+          <t>&gt;50% of liver-metabolized prescription drugs</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>1 t½ = 50% · 2 = 75% · 4 = &gt;90%</t>
+          <t>Active transporters move more drug into tubule</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Phenytoin, ethanol, aspirin</t>
+          <t>Slows CYP → substrate level ↑ → toxicity risk</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Switch to prasugrel or ticagrelor</t>
+          <t>Antidepressants, opioids — codeine activation</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -7912,27 +7912,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>CYP2C19 PM on clopidogrel: which is right?</t>
+          <t>Acetaminophen antidote: which is right?</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Some large or protein-bound drugs</t>
+          <t>N-acetylcysteine within 8–16 h</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>50% / 25% / 12.5% / 6.25% / 3.125%</t>
+          <t>1 t½ = 50% · 2 = 75% · 4 = &gt;90%</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
+          <t>Phenytoin, ethanol, aspirin</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
           <t>Switch to prasugrel or ticagrelor</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Volatile agents (anesthetic gases)</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -7950,27 +7950,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>HLA-B*57:01: which is right?</t>
+          <t>CYP2C19 PM on clopidogrel: which is right?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Abacavir hypersensitivity</t>
+          <t>Some large or protein-bound drugs</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Vd × target concentration</t>
+          <t>50% / 25% / 12.5% / 6.25% / 3.125%</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>C(t) = C₀ x (1/2)^(t/t½)</t>
+          <t>Switch to prasugrel or ticagrelor</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>After about 5 half-lives</t>
+          <t>Volatile agents (anesthetic gases)</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -7978,7 +7978,311 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>112</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>HLA-B*57:01: which is right?</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Abacavir hypersensitivity</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Vd × target concentration</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>C(t) = C₀ x (1/2)^(t/t½)</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>After about 5 half-lives</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>20</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
           <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>113</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Extraction ratio: which is right?</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Traps ionized drug in tubule, blocks reabsorption</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Hepatic CL ÷ hepatic blood flow; F ≈ f × (1 − ER)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Ongoing dose to stay in range; based on clearance</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Simvastatin myopathy: lower dose or another statin</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>30</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>114</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Maintenance dosing rate: which is right?</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Severe hypersensitivity to allopurinol</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>CL × target concentration (÷ F orally)</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Minor; breast milk matters in lactation</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Free (unbound) drug, by molecular size</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>20</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>115</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Average steady-state level: which is right?</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Vd × target concentration</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>C(t) = C₀ x (1/2)^(t/t½)</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Set by clearance alone</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>After about 5 half-lives</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>20</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>116</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>CYP450 machinery: which is right?</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>↑ Toxicity with thiopurines (azathioprine)</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Inhibitor: 240% of baseline; inducer: 42%</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Competitive (not irreversible) antagonism</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>P450 + reductase + NADPH + O₂ (smooth ER)</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>30</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>117</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Smoking: which is right?</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>t½ = 0.7 × Vd / CL</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>C(t) = C₀ x (1/2)^(t/t½)</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Induces CYP1A (AhR)</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Set by clearance alone</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>20</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>118</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Digoxin level timing: which is right?</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Abacavir hypersensitivity</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Vd × target concentration</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>At least 6 h after the dose</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Phenytoin, ethanol, aspirin</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>20</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>119</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>SLCO1B1 variant: which is right?</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Review CYP450 interactions with current medications</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Ongoing dose to stay in range; based on clearance</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Level ↑ and toxicity risk ↑ — especially dangerous</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Simvastatin myopathy: lower dose or another statin</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>30</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>

--- a/docs/sketch/kahoot/unit1_L02.xlsx
+++ b/docs/sketch/kahoot/unit1_L02.xlsx
@@ -1589,7 +1589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA127"/>
+  <dimension ref="A1:AA142"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13"/>
   <cols>
     <col width="12.5" customWidth="1" min="1" max="1"/>
@@ -5404,27 +5404,27 @@
       </c>
       <c r="B71" s="16" t="inlineStr">
         <is>
-          <t>Using Figure 7, approximately what percentage of the original drug concentration remains after 3 half-lives (3 t½)?</t>
+          <t>A patient on a narrow-TI CYP3A4 substrate starts a strong CYP3A4 inhibitor. Most likely consequence?</t>
         </is>
       </c>
       <c r="C71" s="16" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>No change, since CYP3A4 only affects Phase II metabolism</t>
         </is>
       </c>
       <c r="D71" s="16" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>Increased substrate drug level and increased toxicity risk</t>
         </is>
       </c>
       <c r="E71" s="16" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>Increased renal clearance of the substrate drug</t>
         </is>
       </c>
       <c r="F71" s="16" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>Decreased substrate drug level and reduced effect</t>
         </is>
       </c>
       <c r="G71" s="14" t="n">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H71" s="18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I71" s="1" t="n"/>
@@ -5461,27 +5461,27 @@
       </c>
       <c r="B72" s="16" t="inlineStr">
         <is>
-          <t>Approximately how many half-lives are required for a drug to reach steady state with regular, repeated dosing?</t>
+          <t>New CKD drops the eGFR. For a mainly renally eliminated drug, which dosing change fits best?</t>
         </is>
       </c>
       <c r="C72" s="16" t="inlineStr">
         <is>
-          <t>8–10</t>
+          <t>Increase the dose</t>
         </is>
       </c>
       <c r="D72" s="16" t="inlineStr">
         <is>
-          <t>4–5</t>
+          <t>Decrease the dose and/or extend the dosing interval</t>
         </is>
       </c>
       <c r="E72" s="16" t="inlineStr">
         <is>
-          <t>Steady state is reached immediately after the first dose</t>
+          <t>No adjustment is needed</t>
         </is>
       </c>
       <c r="F72" s="16" t="inlineStr">
         <is>
-          <t>1–2</t>
+          <t>Switch to IV administration only</t>
         </is>
       </c>
       <c r="G72" s="14" t="n">
@@ -5518,27 +5518,27 @@
       </c>
       <c r="B73" s="16" t="inlineStr">
         <is>
-          <t>A heavy smoker on a CYP1A2-metabolized drug quits smoking abruptly. What should the PA anticipate?</t>
+          <t>Using Figure 7, approximately what percentage of the original drug concentration remains after 3 half-lives (3 t½)?</t>
         </is>
       </c>
       <c r="C73" s="16" t="inlineStr">
         <is>
-          <t>Drug levels will fall because metabolism speeds up</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="D73" s="16" t="inlineStr">
         <is>
-          <t>No change, since smoking affects only the lungs</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="E73" s="16" t="inlineStr">
         <is>
-          <t>The drug becomes a prodrug that needs activation</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F73" s="16" t="inlineStr">
         <is>
-          <t>Drug levels may rise as CYP1A induction fades</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="G73" s="14" t="n">
@@ -5575,27 +5575,27 @@
       </c>
       <c r="B74" s="16" t="inlineStr">
         <is>
-          <t>Which renal process REDUCES the net elimination of a drug?</t>
+          <t>Approximately how many half-lives are required for a drug to reach steady state with regular, repeated dosing?</t>
         </is>
       </c>
       <c r="C74" s="16" t="inlineStr">
         <is>
-          <t>Filtration of drug based on molecular size</t>
+          <t>8–10</t>
         </is>
       </c>
       <c r="D74" s="16" t="inlineStr">
         <is>
-          <t>Excretion of volatile agents by the lungs</t>
+          <t>4–5</t>
         </is>
       </c>
       <c r="E74" s="16" t="inlineStr">
         <is>
-          <t>Passive reabsorption of lipophilic, un-ionized drug</t>
+          <t>Steady state is reached immediately after the first dose</t>
         </is>
       </c>
       <c r="F74" s="16" t="inlineStr">
         <is>
-          <t>Glomerular filtration of free, unbound drug</t>
+          <t>1–2</t>
         </is>
       </c>
       <c r="G74" s="14" t="n">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="H74" s="18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I74" s="1" t="n"/>
@@ -5632,27 +5632,27 @@
       </c>
       <c r="B75" s="16" t="inlineStr">
         <is>
-          <t>Which statement correctly pairs each dose type with the parameter it is based on?</t>
+          <t>Before any new prescription, which check most directly prevents a predictable drug-drug interaction?</t>
         </is>
       </c>
       <c r="C75" s="16" t="inlineStr">
         <is>
-          <t>Both loading and maintenance doses are based on half-life alone</t>
+          <t>Confirming the drug’s brand name</t>
         </is>
       </c>
       <c r="D75" s="16" t="inlineStr">
         <is>
-          <t>Loading dose is based on Vd; maintenance dose is based on clearance</t>
+          <t>Reviewing CYP450 interactions with the patient’s current medications</t>
         </is>
       </c>
       <c r="E75" s="16" t="inlineStr">
         <is>
-          <t>Loading dose is based on clearance; maintenance dose is based on Vd</t>
+          <t>Checking the drug’s chemical name</t>
         </is>
       </c>
       <c r="F75" s="16" t="inlineStr">
         <is>
-          <t>Both loading and maintenance doses are based on clearance alone</t>
+          <t>Reviewing the drug’s half-life alone</t>
         </is>
       </c>
       <c r="G75" s="14" t="n">
@@ -5689,27 +5689,27 @@
       </c>
       <c r="B76" s="16" t="inlineStr">
         <is>
-          <t>A patient is about to start azathioprine. Testing shows TPMT deficiency. What is the main clinical concern?</t>
+          <t>Drug A: high potency, low efficacy. For maximum symptom relief, which factor matters more?</t>
         </is>
       </c>
       <c r="C76" s="16" t="inlineStr">
         <is>
-          <t>Severe HLA-associated hypersensitivity to the drug</t>
+          <t>Potency</t>
         </is>
       </c>
       <c r="D76" s="16" t="inlineStr">
         <is>
-          <t>No concern, since genotype never affects therapy</t>
+          <t>Efficacy</t>
         </is>
       </c>
       <c r="E76" s="16" t="inlineStr">
         <is>
-          <t>Increased risk of toxicity from the thiopurine drug</t>
+          <t>Both matter equally</t>
         </is>
       </c>
       <c r="F76" s="16" t="inlineStr">
         <is>
-          <t>Faster CYP2D6 metabolism of the drug and lost effect</t>
+          <t>Neither predicts clinical benefit</t>
         </is>
       </c>
       <c r="G76" s="14" t="n">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="H76" s="18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I76" s="1" t="n"/>
@@ -5746,27 +5746,27 @@
       </c>
       <c r="B77" s="16" t="inlineStr">
         <is>
-          <t>Which pairing of a genetic variant with the drug it most affects is correct?</t>
+          <t>A renally cleared, narrow-TI drug is given in CKD with no dose change. Which two effects follow?</t>
         </is>
       </c>
       <c r="C77" s="16" t="inlineStr">
         <is>
-          <t>TPMT variation — codeine activation</t>
+          <t>Increased half-life and increased concentration</t>
         </is>
       </c>
       <c r="D77" s="16" t="inlineStr">
         <is>
-          <t>CYP2C19 variation — clopidogrel activation</t>
+          <t>No change in either parameter</t>
         </is>
       </c>
       <c r="E77" s="16" t="inlineStr">
         <is>
-          <t>HLA-B*5801 — clopidogrel activation</t>
+          <t>Increased clearance and decreased Vd</t>
         </is>
       </c>
       <c r="F77" s="16" t="inlineStr">
         <is>
-          <t>CYP2D6 variation — azathioprine toxicity</t>
+          <t>Decreased half-life and decreased concentration</t>
         </is>
       </c>
       <c r="G77" s="14" t="n">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="H77" s="18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I77" s="1" t="n"/>
@@ -5803,27 +5803,27 @@
       </c>
       <c r="B78" s="16" t="inlineStr">
         <is>
-          <t>Which statement about using pharmacogenomic results best matches the lecture's personalized-pharmacotherapy model?</t>
+          <t>A CYP inducer is started in a patient on a substrate of that enzyme. What happens to the substrate?</t>
         </is>
       </c>
       <c r="C78" s="16" t="inlineStr">
         <is>
-          <t>Genotype is one input alongside phenotype, disease, and other drugs</t>
+          <t>Increases, raising toxicity risk</t>
         </is>
       </c>
       <c r="D78" s="16" t="inlineStr">
         <is>
-          <t>Genotype alone should determine both the drug and its dose</t>
+          <t>Decreases, risking therapeutic failure</t>
         </is>
       </c>
       <c r="E78" s="16" t="inlineStr">
         <is>
-          <t>Genotype matters only for drugs that are given by the IV route</t>
+          <t>Drug B’s route of elimination changes to biliary</t>
         </is>
       </c>
       <c r="F78" s="16" t="inlineStr">
         <is>
-          <t>Genotype affects adverse-reaction risk but never drug metabolism</t>
+          <t>No change</t>
         </is>
       </c>
       <c r="G78" s="14" t="n">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="H78" s="18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I78" s="1" t="n"/>
@@ -5860,27 +5860,27 @@
       </c>
       <c r="B79" s="16" t="inlineStr">
         <is>
-          <t>NAPQI: which is right?</t>
+          <t>Which PK parameter most directly sets how long a drug takes to reach steady state?</t>
         </is>
       </c>
       <c r="C79" s="16" t="inlineStr">
         <is>
-          <t>Toxic metabolite from acetaminophen via normal Phase I metabolism</t>
+          <t>Bioavailability</t>
         </is>
       </c>
       <c r="D79" s="16" t="inlineStr">
         <is>
-          <t>Phase I often first — but some drugs go straight to conjugation</t>
+          <t>Chemical name</t>
         </is>
       </c>
       <c r="E79" s="16" t="inlineStr">
         <is>
-          <t>Time for plasma concentration to fall 50%; set by clearance + Vd</t>
+          <t>Half-life</t>
         </is>
       </c>
       <c r="F79" s="16" t="inlineStr">
         <is>
-          <t>Clearance ↓ → t½ ↑ → concentration ↑ → time to steady state ↑</t>
+          <t>Route of administration</t>
         </is>
       </c>
       <c r="G79" s="14" t="n">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="H79" s="18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I79" s="1" t="n"/>
@@ -5917,27 +5917,27 @@
       </c>
       <c r="B80" s="16" t="inlineStr">
         <is>
-          <t>Phase order: which is right?</t>
+          <t>Checking indication, contraindications, organ function, interactions and monitoring reflects:</t>
         </is>
       </c>
       <c r="C80" s="16" t="inlineStr">
         <is>
-          <t>Phase I often first — but some drugs go straight to conjugation</t>
+          <t>Phase IV surveillance</t>
         </is>
       </c>
       <c r="D80" s="16" t="inlineStr">
         <is>
-          <t>Toxic metabolite from acetaminophen via normal Phase I metabolism</t>
+          <t>Receptor pharmacology alone</t>
         </is>
       </c>
       <c r="E80" s="16" t="inlineStr">
         <is>
-          <t>Clearance ↓ → t½ ↑ → concentration ↑ → time to steady state ↑</t>
+          <t>Pharmacogenomic testing</t>
         </is>
       </c>
       <c r="F80" s="16" t="inlineStr">
         <is>
-          <t>Time for plasma concentration to fall 50%; set by clearance + Vd</t>
+          <t>The clinical decision-making framework</t>
         </is>
       </c>
       <c r="G80" s="14" t="n">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="H80" s="18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I80" s="1" t="n"/>
@@ -5974,27 +5974,27 @@
       </c>
       <c r="B81" s="16" t="inlineStr">
         <is>
-          <t>CYP enzyme inhibition: which is right?</t>
+          <t>Glucuronidation attaches a polar group to a drug. Which statement best describes this step?</t>
         </is>
       </c>
       <c r="C81" s="16" t="inlineStr">
         <is>
-          <t>&gt;50% of liver-metabolized prescription drugs</t>
+          <t>A CYP450-driven hydrolysis that always precedes any Phase II reaction</t>
         </is>
       </c>
       <c r="D81" s="16" t="inlineStr">
         <is>
-          <t>Slows CYP → substrate level ↑ → toxicity risk</t>
+          <t>A reduction reaction that converts a prodrug into its active form</t>
         </is>
       </c>
       <c r="E81" s="16" t="inlineStr">
         <is>
-          <t>Antidepressants, opioids — codeine activation</t>
+          <t>A Phase II conjugation that makes the drug more water-soluble for excretion</t>
         </is>
       </c>
       <c r="F81" s="16" t="inlineStr">
         <is>
-          <t>Active transporters move more drug into tubule</t>
+          <t>A Phase II reaction that makes the drug more lipophilic and longer-acting</t>
         </is>
       </c>
       <c r="G81" s="14" t="n">
@@ -6002,7 +6002,7 @@
       </c>
       <c r="H81" s="18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I81" s="1" t="n"/>
@@ -6031,35 +6031,35 @@
       </c>
       <c r="B82" s="16" t="inlineStr">
         <is>
-          <t>CYP enzyme induction: which is right?</t>
+          <t>6 hours after a large acetaminophen overdose, labs pending. Which treatment best protects the liver?</t>
         </is>
       </c>
       <c r="C82" s="16" t="inlineStr">
         <is>
-          <t>Genotype + phenotype + disease state + other medications</t>
+          <t>Protamine to bind and neutralize the circulating drug</t>
         </is>
       </c>
       <c r="D82" s="16" t="inlineStr">
         <is>
-          <t>More CYP made → substrate level ↓ → therapeutic failure</t>
+          <t>Waiting for levels before giving any treatment at all</t>
         </is>
       </c>
       <c r="E82" s="16" t="inlineStr">
         <is>
-          <t>Intake = elimination; ~4–5 half-lives, regardless of dose</t>
+          <t>Sodium bicarbonate to alkalinize the urine and speed excretion</t>
         </is>
       </c>
       <c r="F82" s="16" t="inlineStr">
         <is>
-          <t>Clopidogrel activation; some antidepressant/PPI dosing</t>
+          <t>N-acetylcysteine, started within the 8–16 hour window</t>
         </is>
       </c>
       <c r="G82" s="14" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H82" s="18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I82" s="1" t="n"/>
@@ -6088,35 +6088,35 @@
       </c>
       <c r="B83" s="16" t="inlineStr">
         <is>
-          <t>Figure 6 values: which is right?</t>
+          <t>A heavy smoker on a CYP1A2-metabolized drug quits smoking abruptly. What should the PA anticipate?</t>
         </is>
       </c>
       <c r="C83" s="16" t="inlineStr">
         <is>
-          <t>↑ Toxicity with thiopurines (azathioprine)</t>
+          <t>Drug levels will fall because metabolism speeds up</t>
         </is>
       </c>
       <c r="D83" s="16" t="inlineStr">
         <is>
-          <t>Inhibitor: 240% of baseline; inducer: 42%</t>
+          <t>No change, since smoking affects only the lungs</t>
         </is>
       </c>
       <c r="E83" s="16" t="inlineStr">
         <is>
-          <t>Competitive (not irreversible) antagonism</t>
+          <t>The drug becomes a prodrug that needs activation</t>
         </is>
       </c>
       <c r="F83" s="16" t="inlineStr">
         <is>
-          <t>P450 + reductase + NADPH + O₂ (smooth ER)</t>
+          <t>Drug levels may rise as CYP1A induction fades</t>
         </is>
       </c>
       <c r="G83" s="14" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H83" s="18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I83" s="1" t="n"/>
@@ -6145,27 +6145,27 @@
       </c>
       <c r="B84" s="16" t="inlineStr">
         <is>
-          <t>CYP3A4 inhibitor + narrow-TI substrate: which is right?</t>
+          <t>After an aspirin overdose, the team alkalinizes the urine. How does that speed elimination?</t>
         </is>
       </c>
       <c r="C84" s="16" t="inlineStr">
         <is>
-          <t>Simvastatin myopathy: lower dose or another statin</t>
+          <t>It traps ionized drug in the tubule, blocking its reabsorption</t>
         </is>
       </c>
       <c r="D84" s="16" t="inlineStr">
         <is>
-          <t>Ongoing dose to stay in range; based on clearance</t>
+          <t>It activates tubular transporters that secrete the drug</t>
         </is>
       </c>
       <c r="E84" s="16" t="inlineStr">
         <is>
-          <t>Traps ionized drug in tubule, blocks reabsorption</t>
+          <t>It shifts elimination from the kidney to bile and feces</t>
         </is>
       </c>
       <c r="F84" s="16" t="inlineStr">
         <is>
-          <t>Level ↑ and toxicity risk ↑ — especially dangerous</t>
+          <t>It increases glomerular filtration of protein-bound drug</t>
         </is>
       </c>
       <c r="G84" s="14" t="n">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="H84" s="18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I84" s="1" t="n"/>
@@ -6202,35 +6202,35 @@
       </c>
       <c r="B85" s="16" t="inlineStr">
         <is>
-          <t>Main elimination route: which is right?</t>
+          <t>Which renal process REDUCES the net elimination of a drug?</t>
         </is>
       </c>
       <c r="C85" s="16" t="inlineStr">
         <is>
-          <t>Kidney (most drugs and metabolites)</t>
+          <t>Filtration of drug based on molecular size</t>
         </is>
       </c>
       <c r="D85" s="16" t="inlineStr">
         <is>
-          <t>Volatile agents (anesthetic gases)</t>
+          <t>Excretion of volatile agents by the lungs</t>
         </is>
       </c>
       <c r="E85" s="16" t="inlineStr">
         <is>
-          <t>50% / 25% / 12.5% / 6.25% / 3.125%</t>
+          <t>Passive reabsorption of lipophilic, un-ionized drug</t>
         </is>
       </c>
       <c r="F85" s="16" t="inlineStr">
         <is>
-          <t>100% x (1/2)^(number of half-lives)</t>
+          <t>Glomerular filtration of free, unbound drug</t>
         </is>
       </c>
       <c r="G85" s="14" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H85" s="18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I85" s="1" t="n"/>
@@ -6259,35 +6259,35 @@
       </c>
       <c r="B86" s="16" t="inlineStr">
         <is>
-          <t>Bile / feces: which is right?</t>
+          <t>An IV dose gives a starting level of 100 mg/L; half-life is 6 h. What is the level at 18 h?</t>
         </is>
       </c>
       <c r="C86" s="16" t="inlineStr">
         <is>
-          <t>Some large or protein-bound drugs</t>
+          <t>50 mg/L, with 50% of the drug eliminated</t>
         </is>
       </c>
       <c r="D86" s="16" t="inlineStr">
         <is>
-          <t>50% / 25% / 12.5% / 6.25% / 3.125%</t>
+          <t>12.5 mg/L, with 87.5% of the drug eliminated</t>
         </is>
       </c>
       <c r="E86" s="16" t="inlineStr">
         <is>
-          <t>Volatile agents (anesthetic gases)</t>
+          <t>25 mg/L, with 75% of the drug eliminated</t>
         </is>
       </c>
       <c r="F86" s="16" t="inlineStr">
         <is>
-          <t>Switch to prasugrel or ticagrelor</t>
+          <t>3.125 mg/L, with about 97% eliminated</t>
         </is>
       </c>
       <c r="G86" s="14" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H86" s="18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I86" s="1" t="n"/>
@@ -6316,35 +6316,35 @@
       </c>
       <c r="B87" s="16" t="inlineStr">
         <is>
-          <t>Lungs: which is right?</t>
+          <t>Which statement correctly pairs each dose type with the parameter it is based on?</t>
         </is>
       </c>
       <c r="C87" s="16" t="inlineStr">
         <is>
-          <t>Volatile agents (anesthetic gases)</t>
+          <t>Both loading and maintenance doses are based on half-life alone</t>
         </is>
       </c>
       <c r="D87" s="16" t="inlineStr">
         <is>
-          <t>100% x (1/2)^(number of half-lives)</t>
+          <t>Loading dose is based on Vd; maintenance dose is based on clearance</t>
         </is>
       </c>
       <c r="E87" s="16" t="inlineStr">
         <is>
-          <t>50% / 25% / 12.5% / 6.25% / 3.125%</t>
+          <t>Loading dose is based on clearance; maintenance dose is based on Vd</t>
         </is>
       </c>
       <c r="F87" s="16" t="inlineStr">
         <is>
-          <t>Some large or protein-bound drugs</t>
+          <t>Both loading and maintenance doses are based on clearance alone</t>
         </is>
       </c>
       <c r="G87" s="14" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H87" s="18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I87" s="1" t="n"/>
@@ -6373,35 +6373,35 @@
       </c>
       <c r="B88" s="16" t="inlineStr">
         <is>
-          <t>Sweat / breast milk: which is right?</t>
+          <t>Same daily dose, given every 8 h instead of every 24 h. What happens to the average steady-state level?</t>
         </is>
       </c>
       <c r="C88" s="16" t="inlineStr">
         <is>
-          <t>Free (unbound) drug, by molecular size</t>
+          <t>It stays the same; only peaks and troughs change</t>
         </is>
       </c>
       <c r="D88" s="16" t="inlineStr">
         <is>
-          <t>CL × target concentration (÷ F orally)</t>
+          <t>It depends on Vd, which now changes</t>
         </is>
       </c>
       <c r="E88" s="16" t="inlineStr">
         <is>
-          <t>Minor; breast milk matters in lactation</t>
+          <t>It doubles because half-life gets longer</t>
         </is>
       </c>
       <c r="F88" s="16" t="inlineStr">
         <is>
-          <t>Severe hypersensitivity to allopurinol</t>
+          <t>It triples because doses come more often</t>
         </is>
       </c>
       <c r="G88" s="14" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H88" s="18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I88" s="1" t="n"/>
@@ -6430,35 +6430,35 @@
       </c>
       <c r="B89" s="16" t="inlineStr">
         <is>
-          <t>Glomerular filtration: which is right?</t>
+          <t>A patient is about to start azathioprine. Testing shows TPMT deficiency. What is the main clinical concern?</t>
         </is>
       </c>
       <c r="C89" s="16" t="inlineStr">
         <is>
-          <t>Free (unbound) drug, by molecular size</t>
+          <t>Severe HLA-associated hypersensitivity to the drug</t>
         </is>
       </c>
       <c r="D89" s="16" t="inlineStr">
         <is>
-          <t>Severe hypersensitivity to allopurinol</t>
+          <t>No concern, since genotype never affects therapy</t>
         </is>
       </c>
       <c r="E89" s="16" t="inlineStr">
         <is>
-          <t>CL × target concentration (÷ F orally)</t>
+          <t>Increased risk of toxicity from the thiopurine drug</t>
         </is>
       </c>
       <c r="F89" s="16" t="inlineStr">
         <is>
-          <t>Minor; breast milk matters in lactation</t>
+          <t>Faster CYP2D6 metabolism of the drug and lost effect</t>
         </is>
       </c>
       <c r="G89" s="14" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H89" s="18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I89" s="1" t="n"/>
@@ -6487,27 +6487,27 @@
       </c>
       <c r="B90" s="16" t="inlineStr">
         <is>
-          <t>Tubular secretion: which is right?</t>
+          <t>Which pairing of a genetic variant with the drug it most affects is correct?</t>
         </is>
       </c>
       <c r="C90" s="16" t="inlineStr">
         <is>
-          <t>Slows CYP → substrate level ↑ → toxicity risk</t>
+          <t>TPMT variation — codeine activation</t>
         </is>
       </c>
       <c r="D90" s="16" t="inlineStr">
         <is>
-          <t>Active transporters move more drug into tubule</t>
+          <t>CYP2C19 variation — clopidogrel activation</t>
         </is>
       </c>
       <c r="E90" s="16" t="inlineStr">
         <is>
-          <t>&gt;50% of liver-metabolized prescription drugs</t>
+          <t>HLA-B*5801 — clopidogrel activation</t>
         </is>
       </c>
       <c r="F90" s="16" t="inlineStr">
         <is>
-          <t>Antidepressants, opioids — codeine activation</t>
+          <t>CYP2D6 variation — azathioprine toxicity</t>
         </is>
       </c>
       <c r="G90" s="14" t="n">
@@ -6544,27 +6544,27 @@
       </c>
       <c r="B91" s="16" t="inlineStr">
         <is>
-          <t>Tubular reabsorption: which is right?</t>
+          <t>Which statement about using pharmacogenomic results best matches the lecture's personalized-pharmacotherapy model?</t>
         </is>
       </c>
       <c r="C91" s="16" t="inlineStr">
         <is>
-          <t>Lipophilic, un-ionized drug diffuses back → less elimination</t>
+          <t>Genotype is one input alongside phenotype, disease, and other drugs</t>
         </is>
       </c>
       <c r="D91" s="16" t="inlineStr">
         <is>
-          <t>Clearance ↓ → t½ ↑ → concentration ↑ → time to steady state ↑</t>
+          <t>Genotype alone should determine both the drug and its dose</t>
         </is>
       </c>
       <c r="E91" s="16" t="inlineStr">
         <is>
-          <t>Many antibiotics, digoxin, lithium — adjust dose or interval</t>
+          <t>Genotype matters only for drugs that are given by the IV route</t>
         </is>
       </c>
       <c r="F91" s="16" t="inlineStr">
         <is>
-          <t>Phase I often first — but some drugs go straight to conjugation</t>
+          <t>Genotype affects adverse-reaction risk but never drug metabolism</t>
         </is>
       </c>
       <c r="G91" s="14" t="n">
@@ -6601,35 +6601,35 @@
       </c>
       <c r="B92" s="16" t="inlineStr">
         <is>
-          <t>Alkalinize urine (aspirin overdose): which is right?</t>
+          <t>After a coronary stent, genotyping shows a CYP2C19 poor metabolizer. Which antiplatelet does CPIC support?</t>
         </is>
       </c>
       <c r="C92" s="16" t="inlineStr">
         <is>
-          <t>Traps ionized drug in tubule, blocks reabsorption</t>
+          <t>Clopidogrel at the standard dose with routine follow-up</t>
         </is>
       </c>
       <c r="D92" s="16" t="inlineStr">
         <is>
-          <t>Level ↑ and toxicity risk ↑ — especially dangerous</t>
+          <t>Clopidogrel plus a CYP2C19 inhibitor to raise its level</t>
         </is>
       </c>
       <c r="E92" s="16" t="inlineStr">
         <is>
-          <t>Ongoing dose to stay in range; based on clearance</t>
+          <t>Codeine-free analgesia plus standard-dose clopidogrel</t>
         </is>
       </c>
       <c r="F92" s="16" t="inlineStr">
         <is>
-          <t>Hepatic CL ÷ hepatic blood flow; F ≈ f × (1 − ER)</t>
+          <t>Prasugrel or ticagrelor instead of clopidogrel</t>
         </is>
       </c>
       <c r="G92" s="14" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H92" s="18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I92" s="1" t="n"/>
@@ -6658,35 +6658,35 @@
       </c>
       <c r="B93" s="16" t="inlineStr">
         <is>
-          <t>Renal function estimates: which is right?</t>
+          <t>A new drug weakens a home medication at the same receptor; raising the home dose restores it. This suggests:</t>
         </is>
       </c>
       <c r="C93" s="16" t="inlineStr">
         <is>
-          <t>eGFR and creatinine clearance (CrCl)</t>
+          <t>The new drug is a full agonist itself</t>
         </is>
       </c>
       <c r="D93" s="16" t="inlineStr">
         <is>
-          <t>100% x (1/2)^(number of half-lives)</t>
+          <t>The new drug is a competitive antagonist</t>
         </is>
       </c>
       <c r="E93" s="16" t="inlineStr">
         <is>
-          <t>CL × target concentration (÷ F orally)</t>
+          <t>The home medication has become toxic</t>
         </is>
       </c>
       <c r="F93" s="16" t="inlineStr">
         <is>
-          <t>Kidney (most drugs and metabolites)</t>
+          <t>The new drug is a strong CYP3A4 inducer</t>
         </is>
       </c>
       <c r="G93" s="14" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H93" s="18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I93" s="1" t="n"/>
@@ -6715,27 +6715,27 @@
       </c>
       <c r="B94" s="16" t="inlineStr">
         <is>
-          <t>Renally cleared narrow-TI drugs: which is right?</t>
+          <t>NAPQI: which is right?</t>
         </is>
       </c>
       <c r="C94" s="16" t="inlineStr">
         <is>
+          <t>Toxic metabolite from acetaminophen via normal Phase I metabolism</t>
+        </is>
+      </c>
+      <c r="D94" s="16" t="inlineStr">
+        <is>
+          <t>Phase I often first — but some drugs go straight to conjugation</t>
+        </is>
+      </c>
+      <c r="E94" s="16" t="inlineStr">
+        <is>
+          <t>Time for plasma concentration to fall 50%; set by clearance + Vd</t>
+        </is>
+      </c>
+      <c r="F94" s="16" t="inlineStr">
+        <is>
           <t>Clearance ↓ → t½ ↑ → concentration ↑ → time to steady state ↑</t>
-        </is>
-      </c>
-      <c r="D94" s="16" t="inlineStr">
-        <is>
-          <t>Many antibiotics, digoxin, lithium — adjust dose or interval</t>
-        </is>
-      </c>
-      <c r="E94" s="16" t="inlineStr">
-        <is>
-          <t>Decrease dose and/or extend interval, guided by eGFR/CrCl</t>
-        </is>
-      </c>
-      <c r="F94" s="16" t="inlineStr">
-        <is>
-          <t>Lipophilic, un-ionized drug diffuses back → less elimination</t>
         </is>
       </c>
       <c r="G94" s="14" t="n">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="H94" s="18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I94" s="1" t="n"/>
@@ -6772,27 +6772,27 @@
       </c>
       <c r="B95" s="16" t="inlineStr">
         <is>
-          <t>CKD dosing: which is right?</t>
+          <t>Phase order: which is right?</t>
         </is>
       </c>
       <c r="C95" s="16" t="inlineStr">
         <is>
-          <t>More CYP made → substrate level ↓ → therapeutic failure</t>
+          <t>Phase I often first — but some drugs go straight to conjugation</t>
         </is>
       </c>
       <c r="D95" s="16" t="inlineStr">
         <is>
-          <t>Genotype + phenotype + disease state + other medications</t>
+          <t>Toxic metabolite from acetaminophen via normal Phase I metabolism</t>
         </is>
       </c>
       <c r="E95" s="16" t="inlineStr">
         <is>
-          <t>Intake = elimination; ~4–5 half-lives, regardless of dose</t>
+          <t>Clearance ↓ → t½ ↑ → concentration ↑ → time to steady state ↑</t>
         </is>
       </c>
       <c r="F95" s="16" t="inlineStr">
         <is>
-          <t>Decrease dose and/or extend interval, guided by eGFR/CrCl</t>
+          <t>Time for plasma concentration to fall 50%; set by clearance + Vd</t>
         </is>
       </c>
       <c r="G95" s="14" t="n">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="H95" s="18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I95" s="1" t="n"/>
@@ -6829,27 +6829,27 @@
       </c>
       <c r="B96" s="16" t="inlineStr">
         <is>
-          <t>Half-life (t½): which is right?</t>
+          <t>CYP enzyme inhibition: which is right?</t>
         </is>
       </c>
       <c r="C96" s="16" t="inlineStr">
         <is>
-          <t>Toxic metabolite from acetaminophen via normal Phase I metabolism</t>
+          <t>&gt;50% of liver-metabolized prescription drugs</t>
         </is>
       </c>
       <c r="D96" s="16" t="inlineStr">
         <is>
-          <t>Time for plasma concentration to fall 50%; set by clearance + Vd</t>
+          <t>Slows CYP → substrate level ↑ → toxicity risk</t>
         </is>
       </c>
       <c r="E96" s="16" t="inlineStr">
         <is>
-          <t>Phase I often first — but some drugs go straight to conjugation</t>
+          <t>Antidepressants, opioids — codeine activation</t>
         </is>
       </c>
       <c r="F96" s="16" t="inlineStr">
         <is>
-          <t>Clearance ↓ → t½ ↑ → concentration ↑ → time to steady state ↑</t>
+          <t>Active transporters move more drug into tubule</t>
         </is>
       </c>
       <c r="G96" s="14" t="n">
@@ -6886,35 +6886,35 @@
       </c>
       <c r="B97" s="16" t="inlineStr">
         <is>
-          <t>% remaining formula: which is right?</t>
+          <t>CYP enzyme induction: which is right?</t>
         </is>
       </c>
       <c r="C97" s="16" t="inlineStr">
         <is>
-          <t>Kidney (most drugs and metabolites)</t>
+          <t>Genotype + phenotype + disease state + other medications</t>
         </is>
       </c>
       <c r="D97" s="16" t="inlineStr">
         <is>
-          <t>eGFR and creatinine clearance (CrCl)</t>
+          <t>More CYP made → substrate level ↓ → therapeutic failure</t>
         </is>
       </c>
       <c r="E97" s="16" t="inlineStr">
         <is>
-          <t>50% / 25% / 12.5% / 6.25% / 3.125%</t>
+          <t>Intake = elimination; ~4–5 half-lives, regardless of dose</t>
         </is>
       </c>
       <c r="F97" s="16" t="inlineStr">
         <is>
-          <t>100% x (1/2)^(number of half-lives)</t>
+          <t>Clopidogrel activation; some antidepressant/PPI dosing</t>
         </is>
       </c>
       <c r="G97" s="14" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H97" s="18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I97" s="1" t="n"/>
@@ -6943,35 +6943,35 @@
       </c>
       <c r="B98" s="16" t="inlineStr">
         <is>
-          <t>Concentration formula: which is right?</t>
+          <t>Figure 6 values: which is right?</t>
         </is>
       </c>
       <c r="C98" s="16" t="inlineStr">
         <is>
-          <t>After about 5 half-lives</t>
+          <t>↑ Toxicity with thiopurines (azathioprine)</t>
         </is>
       </c>
       <c r="D98" s="16" t="inlineStr">
         <is>
-          <t>Vd × target concentration</t>
+          <t>Inhibitor: 240% of baseline; inducer: 42%</t>
         </is>
       </c>
       <c r="E98" s="16" t="inlineStr">
         <is>
-          <t>Abacavir hypersensitivity</t>
+          <t>Competitive (not irreversible) antagonism</t>
         </is>
       </c>
       <c r="F98" s="16" t="inlineStr">
         <is>
-          <t>C(t) = C₀ x (1/2)^(t/t½)</t>
+          <t>P450 + reductase + NADPH + O₂ (smooth ER)</t>
         </is>
       </c>
       <c r="G98" s="14" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H98" s="18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I98" s="1" t="n"/>
@@ -7000,35 +7000,35 @@
       </c>
       <c r="B99" s="16" t="inlineStr">
         <is>
-          <t>Remaining after 1/2/3/4/5 t½: which is right?</t>
+          <t>CYP3A4 inhibitor + narrow-TI substrate: which is right?</t>
         </is>
       </c>
       <c r="C99" s="16" t="inlineStr">
         <is>
-          <t>100% x (1/2)^(number of half-lives)</t>
+          <t>Simvastatin myopathy: lower dose or another statin</t>
         </is>
       </c>
       <c r="D99" s="16" t="inlineStr">
         <is>
-          <t>50% / 25% / 12.5% / 6.25% / 3.125%</t>
+          <t>Ongoing dose to stay in range; based on clearance</t>
         </is>
       </c>
       <c r="E99" s="16" t="inlineStr">
         <is>
-          <t>Volatile agents (anesthetic gases)</t>
+          <t>Traps ionized drug in tubule, blocks reabsorption</t>
         </is>
       </c>
       <c r="F99" s="16" t="inlineStr">
         <is>
-          <t>Some large or protein-bound drugs</t>
+          <t>Level ↑ and toxicity risk ↑ — especially dangerous</t>
         </is>
       </c>
       <c r="G99" s="14" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H99" s="18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I99" s="1" t="n"/>
@@ -7057,27 +7057,27 @@
       </c>
       <c r="B100" s="16" t="inlineStr">
         <is>
-          <t>~97% eliminated: which is right?</t>
+          <t>Main elimination route: which is right?</t>
         </is>
       </c>
       <c r="C100" s="16" t="inlineStr">
         <is>
-          <t>Abacavir hypersensitivity</t>
+          <t>Kidney (most drugs and metabolites)</t>
         </is>
       </c>
       <c r="D100" s="16" t="inlineStr">
         <is>
-          <t>Vd × target concentration</t>
+          <t>Volatile agents (anesthetic gases)</t>
         </is>
       </c>
       <c r="E100" s="16" t="inlineStr">
         <is>
-          <t>C(t) = C₀ x (1/2)^(t/t½)</t>
+          <t>50% / 25% / 12.5% / 6.25% / 3.125%</t>
         </is>
       </c>
       <c r="F100" s="16" t="inlineStr">
         <is>
-          <t>After about 5 half-lives</t>
+          <t>100% x (1/2)^(number of half-lives)</t>
         </is>
       </c>
       <c r="G100" s="14" t="n">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="H100" s="18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I100" s="1" t="n"/>
@@ -7114,31 +7114,31 @@
       </c>
       <c r="B101" s="16" t="inlineStr">
         <is>
-          <t>Steady state: which is right?</t>
+          <t>Bile / feces: which is right?</t>
         </is>
       </c>
       <c r="C101" s="16" t="inlineStr">
         <is>
-          <t>Intake = elimination; ~4–5 half-lives, regardless of dose</t>
+          <t>Some large or protein-bound drugs</t>
         </is>
       </c>
       <c r="D101" s="16" t="inlineStr">
         <is>
-          <t>More CYP made → substrate level ↓ → therapeutic failure</t>
+          <t>50% / 25% / 12.5% / 6.25% / 3.125%</t>
         </is>
       </c>
       <c r="E101" s="16" t="inlineStr">
         <is>
-          <t>Decrease dose and/or extend interval, guided by eGFR/CrCl</t>
+          <t>Volatile agents (anesthetic gases)</t>
         </is>
       </c>
       <c r="F101" s="16" t="inlineStr">
         <is>
-          <t>Genotype + phenotype + disease state + other medications</t>
+          <t>Switch to prasugrel or ticagrelor</t>
         </is>
       </c>
       <c r="G101" s="14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H101" s="18" t="inlineStr">
         <is>
@@ -7171,27 +7171,27 @@
       </c>
       <c r="B102" s="16" t="inlineStr">
         <is>
-          <t>Time to steady state set by: which is right?</t>
+          <t>Lungs: which is right?</t>
         </is>
       </c>
       <c r="C102" s="16" t="inlineStr">
         <is>
-          <t>Set by clearance alone</t>
+          <t>Volatile agents (anesthetic gases)</t>
         </is>
       </c>
       <c r="D102" s="16" t="inlineStr">
         <is>
-          <t>Induces CYP1A (AhR)</t>
+          <t>100% x (1/2)^(number of half-lives)</t>
         </is>
       </c>
       <c r="E102" s="16" t="inlineStr">
         <is>
-          <t>t½ = 0.7 × Vd / CL</t>
+          <t>50% / 25% / 12.5% / 6.25% / 3.125%</t>
         </is>
       </c>
       <c r="F102" s="16" t="inlineStr">
         <is>
-          <t>Half-life</t>
+          <t>Some large or protein-bound drugs</t>
         </is>
       </c>
       <c r="G102" s="14" t="n">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="H102" s="18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I102" s="1" t="n"/>
@@ -7228,31 +7228,31 @@
       </c>
       <c r="B103" s="16" t="inlineStr">
         <is>
-          <t>Loading dose: which is right?</t>
+          <t>Sweat / breast milk: which is right?</t>
         </is>
       </c>
       <c r="C103" s="16" t="inlineStr">
         <is>
-          <t>Level ↑ and toxicity risk ↑ — especially dangerous</t>
+          <t>Free (unbound) drug, by molecular size</t>
         </is>
       </c>
       <c r="D103" s="16" t="inlineStr">
         <is>
-          <t>Simvastatin myopathy: lower dose or another statin</t>
+          <t>CL × target concentration (÷ F orally)</t>
         </is>
       </c>
       <c r="E103" s="16" t="inlineStr">
         <is>
-          <t>Larger first dose → target immediately; based on Vd</t>
+          <t>Minor; breast milk matters in lactation</t>
         </is>
       </c>
       <c r="F103" s="16" t="inlineStr">
         <is>
-          <t>Review CYP450 interactions with current medications</t>
+          <t>Severe hypersensitivity to allopurinol</t>
         </is>
       </c>
       <c r="G103" s="14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H103" s="18" t="inlineStr">
         <is>
@@ -7285,35 +7285,35 @@
       </c>
       <c r="B104" s="16" t="inlineStr">
         <is>
-          <t>Maintenance dose: which is right?</t>
+          <t>Glomerular filtration: which is right?</t>
         </is>
       </c>
       <c r="C104" s="16" t="inlineStr">
         <is>
-          <t>Traps ionized drug in tubule, blocks reabsorption</t>
+          <t>Free (unbound) drug, by molecular size</t>
         </is>
       </c>
       <c r="D104" s="16" t="inlineStr">
         <is>
-          <t>Hepatic CL ÷ hepatic blood flow; F ≈ f × (1 − ER)</t>
+          <t>Severe hypersensitivity to allopurinol</t>
         </is>
       </c>
       <c r="E104" s="16" t="inlineStr">
         <is>
-          <t>Simvastatin myopathy: lower dose or another statin</t>
+          <t>CL × target concentration (÷ F orally)</t>
         </is>
       </c>
       <c r="F104" s="16" t="inlineStr">
         <is>
-          <t>Ongoing dose to stay in range; based on clearance</t>
+          <t>Minor; breast milk matters in lactation</t>
         </is>
       </c>
       <c r="G104" s="14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H104" s="18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I104" s="1" t="n"/>
@@ -7342,27 +7342,27 @@
       </c>
       <c r="B105" s="16" t="inlineStr">
         <is>
-          <t>CKD effect on PK: which is right?</t>
+          <t>Tubular secretion: which is right?</t>
         </is>
       </c>
       <c r="C105" s="16" t="inlineStr">
         <is>
-          <t>Phase I often first — but some drugs go straight to conjugation</t>
+          <t>Slows CYP → substrate level ↑ → toxicity risk</t>
         </is>
       </c>
       <c r="D105" s="16" t="inlineStr">
         <is>
-          <t>Clearance ↓ → t½ ↑ → concentration ↑ → time to steady state ↑</t>
+          <t>Active transporters move more drug into tubule</t>
         </is>
       </c>
       <c r="E105" s="16" t="inlineStr">
         <is>
-          <t>Lipophilic, un-ionized drug diffuses back → less elimination</t>
+          <t>&gt;50% of liver-metabolized prescription drugs</t>
         </is>
       </c>
       <c r="F105" s="16" t="inlineStr">
         <is>
-          <t>Many antibiotics, digoxin, lithium — adjust dose or interval</t>
+          <t>Antidepressants, opioids — codeine activation</t>
         </is>
       </c>
       <c r="G105" s="14" t="n">
@@ -7399,27 +7399,27 @@
       </c>
       <c r="B106" s="16" t="inlineStr">
         <is>
-          <t>CYP2D6 variation: which is right?</t>
+          <t>Tubular reabsorption: which is right?</t>
         </is>
       </c>
       <c r="C106" s="16" t="inlineStr">
         <is>
-          <t>Antidepressants, opioids — codeine activation</t>
+          <t>Lipophilic, un-ionized drug diffuses back → less elimination</t>
         </is>
       </c>
       <c r="D106" s="16" t="inlineStr">
         <is>
-          <t>Active transporters move more drug into tubule</t>
+          <t>Clearance ↓ → t½ ↑ → concentration ↑ → time to steady state ↑</t>
         </is>
       </c>
       <c r="E106" s="16" t="inlineStr">
         <is>
-          <t>Slows CYP → substrate level ↑ → toxicity risk</t>
+          <t>Many antibiotics, digoxin, lithium — adjust dose or interval</t>
         </is>
       </c>
       <c r="F106" s="16" t="inlineStr">
         <is>
-          <t>&gt;50% of liver-metabolized prescription drugs</t>
+          <t>Phase I often first — but some drugs go straight to conjugation</t>
         </is>
       </c>
       <c r="G106" s="14" t="n">
@@ -7456,27 +7456,27 @@
       </c>
       <c r="B107" s="16" t="inlineStr">
         <is>
-          <t>CYP2C19 variation: which is right?</t>
+          <t>Alkalinize urine (aspirin overdose): which is right?</t>
         </is>
       </c>
       <c r="C107" s="16" t="inlineStr">
         <is>
-          <t>More CYP made → substrate level ↓ → therapeutic failure</t>
+          <t>Traps ionized drug in tubule, blocks reabsorption</t>
         </is>
       </c>
       <c r="D107" s="16" t="inlineStr">
         <is>
-          <t>Genotype + phenotype + disease state + other medications</t>
+          <t>Level ↑ and toxicity risk ↑ — especially dangerous</t>
         </is>
       </c>
       <c r="E107" s="16" t="inlineStr">
         <is>
-          <t>Clopidogrel activation; some antidepressant/PPI dosing</t>
+          <t>Ongoing dose to stay in range; based on clearance</t>
         </is>
       </c>
       <c r="F107" s="16" t="inlineStr">
         <is>
-          <t>Larger first dose → target immediately; based on Vd</t>
+          <t>Hepatic CL ÷ hepatic blood flow; F ≈ f × (1 − ER)</t>
         </is>
       </c>
       <c r="G107" s="14" t="n">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="H107" s="18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I107" s="1" t="n"/>
@@ -7513,31 +7513,31 @@
       </c>
       <c r="B108" s="16" t="inlineStr">
         <is>
-          <t>TPMT deficiency: which is right?</t>
+          <t>Renal function estimates: which is right?</t>
         </is>
       </c>
       <c r="C108" s="16" t="inlineStr">
         <is>
-          <t>↑ Toxicity with thiopurines (azathioprine)</t>
+          <t>eGFR and creatinine clearance (CrCl)</t>
         </is>
       </c>
       <c r="D108" s="16" t="inlineStr">
         <is>
-          <t>Inhibitor: 240% of baseline; inducer: 42%</t>
+          <t>100% x (1/2)^(number of half-lives)</t>
         </is>
       </c>
       <c r="E108" s="16" t="inlineStr">
         <is>
-          <t>Competitive (not irreversible) antagonism</t>
+          <t>CL × target concentration (÷ F orally)</t>
         </is>
       </c>
       <c r="F108" s="16" t="inlineStr">
         <is>
-          <t>P450 + reductase + NADPH + O₂ (smooth ER)</t>
+          <t>Kidney (most drugs and metabolites)</t>
         </is>
       </c>
       <c r="G108" s="14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H108" s="18" t="inlineStr">
         <is>
@@ -7570,35 +7570,35 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>HLA-B*5801: which is right?</t>
+          <t>Renally cleared narrow-TI drugs: which is right?</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Severe hypersensitivity to allopurinol</t>
+          <t>Clearance ↓ → t½ ↑ → concentration ↑ → time to steady state ↑</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Free (unbound) drug, by molecular size</t>
+          <t>Many antibiotics, digoxin, lithium — adjust dose or interval</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Minor; breast milk matters in lactation</t>
+          <t>Decrease dose and/or extend interval, guided by eGFR/CrCl</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>CL × target concentration (÷ F orally)</t>
+          <t>Lipophilic, un-ionized drug diffuses back → less elimination</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -7608,27 +7608,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Personalized therapy inputs: which is right?</t>
+          <t>CKD dosing: which is right?</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
+          <t>More CYP made → substrate level ↓ → therapeutic failure</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Genotype + phenotype + disease state + other medications</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Intake = elimination; ~4–5 half-lives, regardless of dose</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
           <t>Decrease dose and/or extend interval, guided by eGFR/CrCl</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Genotype + phenotype + disease state + other medications</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>More CYP made → substrate level ↓ → therapeutic failure</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Intake = elimination; ~4–5 half-lives, regardless of dose</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -7646,27 +7646,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Effect weakened, restored by higher agonist dose: which is right?</t>
+          <t>Half-life (t½): which is right?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>P450 + reductase + NADPH + O₂ (smooth ER)</t>
+          <t>Toxic metabolite from acetaminophen via normal Phase I metabolism</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Competitive (not irreversible) antagonism</t>
+          <t>Time for plasma concentration to fall 50%; set by clearance + Vd</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>↑ Toxicity with thiopurines (azathioprine)</t>
+          <t>Phase I often first — but some drugs go straight to conjugation</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Inhibitor: 240% of baseline; inducer: 42%</t>
+          <t>Clearance ↓ → t½ ↑ → concentration ↑ → time to steady state ↑</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -7684,35 +7684,35 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Single best check vs. predictable toxicity: which is right?</t>
+          <t>% remaining formula: which is right?</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Simvastatin myopathy: lower dose or another statin</t>
+          <t>Kidney (most drugs and metabolites)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Review CYP450 interactions with current medications</t>
+          <t>eGFR and creatinine clearance (CrCl)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Larger first dose → target immediately; based on Vd</t>
+          <t>50% / 25% / 12.5% / 6.25% / 3.125%</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Level ↑ and toxicity risk ↑ — especially dangerous</t>
+          <t>100% x (1/2)^(number of half-lives)</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -7722,27 +7722,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>t½ formula: which is right?</t>
+          <t>Concentration formula: which is right?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Induces CYP1A (AhR)</t>
+          <t>After about 5 half-lives</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Set by clearance alone</t>
+          <t>Vd × target concentration</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>t½ = 0.7 × Vd / CL</t>
+          <t>Abacavir hypersensitivity</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>After about 5 half-lives</t>
+          <t>C(t) = C₀ x (1/2)^(t/t½)</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -7750,7 +7750,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -7760,27 +7760,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Loading dose formula: which is right?</t>
+          <t>Remaining after 1/2/3/4/5 t½: which is right?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Vd × target concentration</t>
+          <t>100% x (1/2)^(number of half-lives)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>After about 5 half-lives</t>
+          <t>50% / 25% / 12.5% / 6.25% / 3.125%</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>C(t) = C₀ x (1/2)^(t/t½)</t>
+          <t>Volatile agents (anesthetic gases)</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Abacavir hypersensitivity</t>
+          <t>Some large or protein-bound drugs</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -7798,27 +7798,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>% of steady state: which is right?</t>
+          <t>~97% eliminated: which is right?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>1 t½ = 50% · 2 = 75% · 4 = &gt;90%</t>
+          <t>Abacavir hypersensitivity</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Some large or protein-bound drugs</t>
+          <t>Vd × target concentration</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Switch to prasugrel or ticagrelor</t>
+          <t>C(t) = C₀ x (1/2)^(t/t½)</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>N-acetylcysteine within 8–16 h</t>
+          <t>After about 5 half-lives</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -7836,31 +7836,31 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Saturable elimination: which is right?</t>
+          <t>Steady state: which is right?</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Phenytoin, ethanol, aspirin</t>
+          <t>Intake = elimination; ~4–5 half-lives, regardless of dose</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Abacavir hypersensitivity</t>
+          <t>More CYP made → substrate level ↓ → therapeutic failure</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>At least 6 h after the dose</t>
+          <t>Decrease dose and/or extend interval, guided by eGFR/CrCl</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vd × target concentration</t>
+          <t>Genotype + phenotype + disease state + other medications</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -7874,35 +7874,35 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>CYP3A4 share: which is right?</t>
+          <t>Time to steady state set by: which is right?</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>&gt;50% of liver-metabolized prescription drugs</t>
+          <t>Set by clearance alone</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Active transporters move more drug into tubule</t>
+          <t>Induces CYP1A (AhR)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Slows CYP → substrate level ↑ → toxicity risk</t>
+          <t>t½ = 0.7 × Vd / CL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Antidepressants, opioids — codeine activation</t>
+          <t>Half-life</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -7912,35 +7912,35 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Acetaminophen antidote: which is right?</t>
+          <t>Loading dose: which is right?</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>N-acetylcysteine within 8–16 h</t>
+          <t>Level ↑ and toxicity risk ↑ — especially dangerous</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>1 t½ = 50% · 2 = 75% · 4 = &gt;90%</t>
+          <t>Simvastatin myopathy: lower dose or another statin</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Phenytoin, ethanol, aspirin</t>
+          <t>Larger first dose → target immediately; based on Vd</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Switch to prasugrel or ticagrelor</t>
+          <t>Review CYP450 interactions with current medications</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -7950,35 +7950,35 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>CYP2C19 PM on clopidogrel: which is right?</t>
+          <t>Maintenance dose: which is right?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Some large or protein-bound drugs</t>
+          <t>Traps ionized drug in tubule, blocks reabsorption</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>50% / 25% / 12.5% / 6.25% / 3.125%</t>
+          <t>Hepatic CL ÷ hepatic blood flow; F ≈ f × (1 − ER)</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Switch to prasugrel or ticagrelor</t>
+          <t>Simvastatin myopathy: lower dose or another statin</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Volatile agents (anesthetic gases)</t>
+          <t>Ongoing dose to stay in range; based on clearance</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -7988,35 +7988,35 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>HLA-B*57:01: which is right?</t>
+          <t>CKD effect on PK: which is right?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Abacavir hypersensitivity</t>
+          <t>Phase I often first — but some drugs go straight to conjugation</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Vd × target concentration</t>
+          <t>Clearance ↓ → t½ ↑ → concentration ↑ → time to steady state ↑</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>C(t) = C₀ x (1/2)^(t/t½)</t>
+          <t>Lipophilic, un-ionized drug diffuses back → less elimination</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>After about 5 half-lives</t>
+          <t>Many antibiotics, digoxin, lithium — adjust dose or interval</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -8026,27 +8026,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Extraction ratio: which is right?</t>
+          <t>CYP2D6 variation: which is right?</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Traps ionized drug in tubule, blocks reabsorption</t>
+          <t>Antidepressants, opioids — codeine activation</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Hepatic CL ÷ hepatic blood flow; F ≈ f × (1 − ER)</t>
+          <t>Active transporters move more drug into tubule</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Ongoing dose to stay in range; based on clearance</t>
+          <t>Slows CYP → substrate level ↑ → toxicity risk</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Simvastatin myopathy: lower dose or another statin</t>
+          <t>&gt;50% of liver-metabolized prescription drugs</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -8064,35 +8064,35 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Maintenance dosing rate: which is right?</t>
+          <t>CYP2C19 variation: which is right?</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Severe hypersensitivity to allopurinol</t>
+          <t>More CYP made → substrate level ↓ → therapeutic failure</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>CL × target concentration (÷ F orally)</t>
+          <t>Genotype + phenotype + disease state + other medications</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Minor; breast milk matters in lactation</t>
+          <t>Clopidogrel activation; some antidepressant/PPI dosing</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Free (unbound) drug, by molecular size</t>
+          <t>Larger first dose → target immediately; based on Vd</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -8102,35 +8102,35 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Average steady-state level: which is right?</t>
+          <t>TPMT deficiency: which is right?</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Vd × target concentration</t>
+          <t>↑ Toxicity with thiopurines (azathioprine)</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>C(t) = C₀ x (1/2)^(t/t½)</t>
+          <t>Inhibitor: 240% of baseline; inducer: 42%</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Set by clearance alone</t>
+          <t>Competitive (not irreversible) antagonism</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>After about 5 half-lives</t>
+          <t>P450 + reductase + NADPH + O₂ (smooth ER)</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -8140,35 +8140,35 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>CYP450 machinery: which is right?</t>
+          <t>HLA-B*5801: which is right?</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>↑ Toxicity with thiopurines (azathioprine)</t>
+          <t>Severe hypersensitivity to allopurinol</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Inhibitor: 240% of baseline; inducer: 42%</t>
+          <t>Free (unbound) drug, by molecular size</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Competitive (not irreversible) antagonism</t>
+          <t>Minor; breast milk matters in lactation</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>P450 + reductase + NADPH + O₂ (smooth ER)</t>
+          <t>CL × target concentration (÷ F orally)</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -8178,35 +8178,35 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Smoking: which is right?</t>
+          <t>Personalized therapy inputs: which is right?</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>t½ = 0.7 × Vd / CL</t>
+          <t>Decrease dose and/or extend interval, guided by eGFR/CrCl</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>C(t) = C₀ x (1/2)^(t/t½)</t>
+          <t>Genotype + phenotype + disease state + other medications</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Induces CYP1A (AhR)</t>
+          <t>More CYP made → substrate level ↓ → therapeutic failure</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Set by clearance alone</t>
+          <t>Intake = elimination; ~4–5 half-lives, regardless of dose</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -8216,35 +8216,35 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Digoxin level timing: which is right?</t>
+          <t>Effect weakened, restored by higher agonist dose: which is right?</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Abacavir hypersensitivity</t>
+          <t>P450 + reductase + NADPH + O₂ (smooth ER)</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Vd × target concentration</t>
+          <t>Competitive (not irreversible) antagonism</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>At least 6 h after the dose</t>
+          <t>↑ Toxicity with thiopurines (azathioprine)</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Phenytoin, ethanol, aspirin</t>
+          <t>Inhibitor: 240% of baseline; inducer: 42%</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -8254,33 +8254,603 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SLCO1B1 variant: which is right?</t>
+          <t>Single best check vs. predictable toxicity: which is right?</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
+          <t>Simvastatin myopathy: lower dose or another statin</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
           <t>Review CYP450 interactions with current medications</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Ongoing dose to stay in range; based on clearance</t>
-        </is>
-      </c>
       <c r="E127" t="inlineStr">
         <is>
+          <t>Larger first dose → target immediately; based on Vd</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
           <t>Level ↑ and toxicity risk ↑ — especially dangerous</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Simvastatin myopathy: lower dose or another statin</t>
         </is>
       </c>
       <c r="G127" t="n">
         <v>30</v>
       </c>
       <c r="H127" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>120</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>t½ formula: which is right?</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Induces CYP1A (AhR)</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Set by clearance alone</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>t½ = 0.7 × Vd / CL</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>After about 5 half-lives</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>20</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>121</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Loading dose formula: which is right?</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Vd × target concentration</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>After about 5 half-lives</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>C(t) = C₀ x (1/2)^(t/t½)</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Abacavir hypersensitivity</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>20</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>122</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>% of steady state: which is right?</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>1 t½ = 50% · 2 = 75% · 4 = &gt;90%</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Some large or protein-bound drugs</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Switch to prasugrel or ticagrelor</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>N-acetylcysteine within 8–16 h</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>20</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>123</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Saturable elimination: which is right?</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Phenytoin, ethanol, aspirin</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Abacavir hypersensitivity</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>At least 6 h after the dose</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Vd × target concentration</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>20</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>124</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>CYP3A4 share: which is right?</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>&gt;50% of liver-metabolized prescription drugs</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Active transporters move more drug into tubule</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Slows CYP → substrate level ↑ → toxicity risk</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Antidepressants, opioids — codeine activation</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>30</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>125</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Acetaminophen antidote: which is right?</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>N-acetylcysteine within 8–16 h</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>1 t½ = 50% · 2 = 75% · 4 = &gt;90%</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Phenytoin, ethanol, aspirin</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Switch to prasugrel or ticagrelor</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>20</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>126</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>CYP2C19 PM on clopidogrel: which is right?</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Some large or protein-bound drugs</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>50% / 25% / 12.5% / 6.25% / 3.125%</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Switch to prasugrel or ticagrelor</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Volatile agents (anesthetic gases)</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>20</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>127</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>HLA-B*57:01: which is right?</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Abacavir hypersensitivity</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Vd × target concentration</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>C(t) = C₀ x (1/2)^(t/t½)</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>After about 5 half-lives</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>20</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>128</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Extraction ratio: which is right?</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Traps ionized drug in tubule, blocks reabsorption</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Hepatic CL ÷ hepatic blood flow; F ≈ f × (1 − ER)</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Ongoing dose to stay in range; based on clearance</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Simvastatin myopathy: lower dose or another statin</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>30</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>129</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Maintenance dosing rate: which is right?</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Severe hypersensitivity to allopurinol</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>CL × target concentration (÷ F orally)</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Minor; breast milk matters in lactation</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Free (unbound) drug, by molecular size</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>20</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>130</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Average steady-state level: which is right?</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Vd × target concentration</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>C(t) = C₀ x (1/2)^(t/t½)</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Set by clearance alone</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>After about 5 half-lives</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>20</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>131</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>CYP450 machinery: which is right?</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>↑ Toxicity with thiopurines (azathioprine)</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Inhibitor: 240% of baseline; inducer: 42%</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Competitive (not irreversible) antagonism</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>P450 + reductase + NADPH + O₂ (smooth ER)</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>30</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>132</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Smoking: which is right?</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>t½ = 0.7 × Vd / CL</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>C(t) = C₀ x (1/2)^(t/t½)</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Induces CYP1A (AhR)</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Set by clearance alone</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>20</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>133</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Digoxin level timing: which is right?</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Abacavir hypersensitivity</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Vd × target concentration</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>At least 6 h after the dose</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Phenytoin, ethanol, aspirin</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>20</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>134</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>SLCO1B1 variant: which is right?</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Review CYP450 interactions with current medications</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Ongoing dose to stay in range; based on clearance</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Level ↑ and toxicity risk ↑ — especially dangerous</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Simvastatin myopathy: lower dose or another statin</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>30</v>
+      </c>
+      <c r="H142" t="inlineStr">
         <is>
           <t>4</t>
         </is>

--- a/docs/sketch/kahoot/unit1_L02.xlsx
+++ b/docs/sketch/kahoot/unit1_L02.xlsx
@@ -1589,7 +1589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA142"/>
+  <dimension ref="A1:AA141"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13"/>
   <cols>
     <col width="12.5" customWidth="1" min="1" max="1"/>
@@ -6963,7 +6963,7 @@
       </c>
       <c r="F98" s="16" t="inlineStr">
         <is>
-          <t>P450 + reductase + NADPH + O₂ (smooth ER)</t>
+          <t>Minor; breast milk matters in lactation</t>
         </is>
       </c>
       <c r="G98" s="14" t="n">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="E105" s="16" t="inlineStr">
         <is>
-          <t>&gt;50% of liver-metabolized prescription drugs</t>
+          <t>High ER → low oral bioavailability (first pass)</t>
         </is>
       </c>
       <c r="F105" s="16" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="F107" s="16" t="inlineStr">
         <is>
-          <t>Hepatic CL ÷ hepatic blood flow; F ≈ f × (1 − ER)</t>
+          <t>Simvastatin myopathy: lower dose or another statin</t>
         </is>
       </c>
       <c r="G107" s="14" t="n">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Induces CYP1A (AhR)</t>
+          <t>Induces CYP1A</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7960,17 +7960,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Hepatic CL ÷ hepatic blood flow; F ≈ f × (1 − ER)</t>
+          <t>Simvastatin myopathy: lower dose or another statin</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Simvastatin myopathy: lower dose or another statin</t>
+          <t>Ongoing dose to stay in range; based on clearance</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ongoing dose to stay in range; based on clearance</t>
+          <t>Level ↑ and toxicity risk ↑ — especially dangerous</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -8112,17 +8112,17 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
+          <t>&gt;50% of liver-metabolized prescription drugs</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
           <t>Inhibitor: 240% of baseline; inducer: 42%</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="F123" t="inlineStr">
         <is>
           <t>Competitive (not irreversible) antagonism</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>P450 + reductase + NADPH + O₂ (smooth ER)</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -8221,22 +8221,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>P450 + reductase + NADPH + O₂ (smooth ER)</t>
+          <t>Competitive (not irreversible) antagonism</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Competitive (not irreversible) antagonism</t>
+          <t>↑ Toxicity with thiopurines (azathioprine)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>↑ Toxicity with thiopurines (azathioprine)</t>
+          <t>Inhibitor: 240% of baseline; inducer: 42%</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Inhibitor: 240% of baseline; inducer: 42%</t>
+          <t>Minor; breast milk matters in lactation</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -8297,12 +8297,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Induces CYP1A (AhR)</t>
+          <t>Set by clearance alone</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Set by clearance alone</t>
+          <t>Induces CYP1A</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8606,17 +8606,17 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Hepatic CL ÷ hepatic blood flow; F ≈ f × (1 − ER)</t>
+          <t>Active transporters move more drug into tubule</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Ongoing dose to stay in range; based on clearance</t>
+          <t>Antidepressants, opioids — codeine activation</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Simvastatin myopathy: lower dose or another statin</t>
+          <t>High ER → low oral bioavailability (first pass)</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -8710,35 +8710,35 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>CYP450 machinery: which is right?</t>
+          <t>Smoking: which is right?</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>↑ Toxicity with thiopurines (azathioprine)</t>
+          <t>Induces CYP1A</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Inhibitor: 240% of baseline; inducer: 42%</t>
+          <t>t½ = 0.7 × Vd / CL</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Competitive (not irreversible) antagonism</t>
+          <t>Half-life</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>P450 + reductase + NADPH + O₂ (smooth ER)</t>
+          <t>Set by clearance alone</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -8748,27 +8748,27 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Smoking: which is right?</t>
+          <t>Digoxin level timing: which is right?</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>t½ = 0.7 × Vd / CL</t>
+          <t>Abacavir hypersensitivity</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>C(t) = C₀ x (1/2)^(t/t½)</t>
+          <t>Vd × target concentration</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Induces CYP1A (AhR)</t>
+          <t>At least 6 h after the dose</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Set by clearance alone</t>
+          <t>Phenytoin, ethanol, aspirin</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -8786,71 +8786,33 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Digoxin level timing: which is right?</t>
+          <t>SLCO1B1 variant: which is right?</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Abacavir hypersensitivity</t>
+          <t>Review CYP450 interactions with current medications</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Vd × target concentration</t>
+          <t>Ongoing dose to stay in range; based on clearance</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>At least 6 h after the dose</t>
+          <t>Level ↑ and toxicity risk ↑ — especially dangerous</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Phenytoin, ethanol, aspirin</t>
+          <t>Simvastatin myopathy: lower dose or another statin</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H141" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="n">
-        <v>134</v>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>SLCO1B1 variant: which is right?</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Review CYP450 interactions with current medications</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>Ongoing dose to stay in range; based on clearance</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Level ↑ and toxicity risk ↑ — especially dangerous</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>Simvastatin myopathy: lower dose or another statin</t>
-        </is>
-      </c>
-      <c r="G142" t="n">
-        <v>30</v>
-      </c>
-      <c r="H142" t="inlineStr">
         <is>
           <t>4</t>
         </is>
